--- a/artfynd/A 50796-2025 artfynd.xlsx
+++ b/artfynd/A 50796-2025 artfynd.xlsx
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129806156</v>
+        <v>129806166</v>
       </c>
       <c r="B6" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616164</v>
+        <v>616060</v>
       </c>
       <c r="R6" t="n">
-        <v>6647189</v>
+        <v>6646944</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1139,6 +1139,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129806166</v>
+        <v>129806156</v>
       </c>
       <c r="B7" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616060</v>
+        <v>616164</v>
       </c>
       <c r="R7" t="n">
-        <v>6646944</v>
+        <v>6647189</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1236,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,7 +1267,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129806173</v>
+        <v>129806176</v>
       </c>
       <c r="B8" t="n">
         <v>79081</v>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616036</v>
+        <v>616099</v>
       </c>
       <c r="R8" t="n">
-        <v>6646801</v>
+        <v>6647122</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129806176</v>
+        <v>129806173</v>
       </c>
       <c r="B9" t="n">
         <v>79081</v>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616099</v>
+        <v>616036</v>
       </c>
       <c r="R9" t="n">
-        <v>6647122</v>
+        <v>6646801</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129806172</v>
+        <v>129806195</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>96263</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615803</v>
+        <v>615759</v>
       </c>
       <c r="R12" t="n">
-        <v>6646576</v>
+        <v>6646541</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129806195</v>
+        <v>129806172</v>
       </c>
       <c r="B13" t="n">
-        <v>96263</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615759</v>
+        <v>615803</v>
       </c>
       <c r="R13" t="n">
-        <v>6646541</v>
+        <v>6646576</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129806147</v>
+        <v>129806175</v>
       </c>
       <c r="B14" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615859</v>
+        <v>615799</v>
       </c>
       <c r="R14" t="n">
-        <v>6646550</v>
+        <v>6646623</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129806175</v>
+        <v>129806147</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615799</v>
+        <v>615859</v>
       </c>
       <c r="R16" t="n">
-        <v>6646623</v>
+        <v>6646550</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2242,32 +2242,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129806158</v>
+        <v>129806194</v>
       </c>
       <c r="B18" t="n">
-        <v>97645</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616104</v>
+        <v>616079</v>
       </c>
       <c r="R18" t="n">
-        <v>6646974</v>
+        <v>6647068</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2339,32 +2339,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129806194</v>
+        <v>129806160</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616079</v>
+        <v>616150</v>
       </c>
       <c r="R19" t="n">
-        <v>6647068</v>
+        <v>6646959</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2410,6 +2410,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>10. 30st</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2436,32 +2441,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129806160</v>
+        <v>129806158</v>
       </c>
       <c r="B20" t="n">
-        <v>98774</v>
+        <v>97645</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2471,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>616150</v>
+        <v>616104</v>
       </c>
       <c r="R20" t="n">
-        <v>6646959</v>
+        <v>6646974</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2507,11 +2512,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>10. 30st</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2538,32 +2538,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129806152</v>
+        <v>129806170</v>
       </c>
       <c r="B21" t="n">
-        <v>57896</v>
+        <v>105840</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615859</v>
+        <v>616130</v>
       </c>
       <c r="R21" t="n">
-        <v>6646562</v>
+        <v>6647159</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2635,32 +2635,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129806165</v>
+        <v>129806152</v>
       </c>
       <c r="B22" t="n">
-        <v>98774</v>
+        <v>57896</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>616079</v>
+        <v>615859</v>
       </c>
       <c r="R22" t="n">
-        <v>6646998</v>
+        <v>6646562</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2706,11 +2706,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2737,32 +2732,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129806170</v>
+        <v>129806165</v>
       </c>
       <c r="B23" t="n">
-        <v>105840</v>
+        <v>98774</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2772,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>616130</v>
+        <v>616079</v>
       </c>
       <c r="R23" t="n">
-        <v>6647159</v>
+        <v>6646998</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2808,6 +2803,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3436,32 +3436,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129806168</v>
+        <v>129806146</v>
       </c>
       <c r="B30" t="n">
-        <v>98774</v>
+        <v>91557</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615857</v>
+        <v>615873</v>
       </c>
       <c r="R30" t="n">
-        <v>6646561</v>
+        <v>6646602</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3507,11 +3507,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3538,32 +3533,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129806146</v>
+        <v>129806155</v>
       </c>
       <c r="B31" t="n">
-        <v>91557</v>
+        <v>57733</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3573,10 +3568,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615873</v>
+        <v>615771</v>
       </c>
       <c r="R31" t="n">
-        <v>6646602</v>
+        <v>6646537</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3635,32 +3630,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129806155</v>
+        <v>129806168</v>
       </c>
       <c r="B32" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3670,10 +3665,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615771</v>
+        <v>615857</v>
       </c>
       <c r="R32" t="n">
-        <v>6646537</v>
+        <v>6646561</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3706,6 +3701,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 50796-2025 artfynd.xlsx
+++ b/artfynd/A 50796-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129806192</v>
+        <v>129806163</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616113</v>
+        <v>615949</v>
       </c>
       <c r="R2" t="n">
-        <v>6647153</v>
+        <v>6646761</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129806174</v>
+        <v>129806192</v>
       </c>
       <c r="B3" t="n">
         <v>79081</v>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616053</v>
+        <v>616113</v>
       </c>
       <c r="R3" t="n">
-        <v>6646812</v>
+        <v>6647153</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129806163</v>
+        <v>129806174</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615949</v>
+        <v>616053</v>
       </c>
       <c r="R4" t="n">
-        <v>6646761</v>
+        <v>6646812</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129806195</v>
+        <v>129806172</v>
       </c>
       <c r="B12" t="n">
-        <v>96263</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615759</v>
+        <v>615803</v>
       </c>
       <c r="R12" t="n">
-        <v>6646541</v>
+        <v>6646576</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129806172</v>
+        <v>129806195</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>96263</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615803</v>
+        <v>615759</v>
       </c>
       <c r="R13" t="n">
-        <v>6646576</v>
+        <v>6646541</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2339,32 +2339,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129806160</v>
+        <v>129806158</v>
       </c>
       <c r="B19" t="n">
-        <v>98774</v>
+        <v>97645</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616150</v>
+        <v>616104</v>
       </c>
       <c r="R19" t="n">
-        <v>6646959</v>
+        <v>6646974</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2410,11 +2410,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>10. 30st</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2441,32 +2436,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129806158</v>
+        <v>129806160</v>
       </c>
       <c r="B20" t="n">
-        <v>97645</v>
+        <v>98774</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>616104</v>
+        <v>616150</v>
       </c>
       <c r="R20" t="n">
-        <v>6646974</v>
+        <v>6646959</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2512,6 +2507,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>10. 30st</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2538,32 +2538,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129806170</v>
+        <v>129806165</v>
       </c>
       <c r="B21" t="n">
-        <v>105840</v>
+        <v>98774</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>616130</v>
+        <v>616079</v>
       </c>
       <c r="R21" t="n">
-        <v>6647159</v>
+        <v>6646998</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2609,6 +2609,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2635,32 +2640,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129806152</v>
+        <v>129806170</v>
       </c>
       <c r="B22" t="n">
-        <v>57896</v>
+        <v>105840</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>615859</v>
+        <v>616130</v>
       </c>
       <c r="R22" t="n">
-        <v>6646562</v>
+        <v>6647159</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2732,7 +2737,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129806165</v>
+        <v>129806167</v>
       </c>
       <c r="B23" t="n">
         <v>98774</v>
@@ -2767,10 +2772,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>616079</v>
+        <v>615953</v>
       </c>
       <c r="R23" t="n">
-        <v>6646998</v>
+        <v>6646752</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2807,7 +2812,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2834,32 +2839,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129806167</v>
+        <v>129806152</v>
       </c>
       <c r="B24" t="n">
-        <v>98774</v>
+        <v>57896</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2869,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615953</v>
+        <v>615859</v>
       </c>
       <c r="R24" t="n">
-        <v>6646752</v>
+        <v>6646562</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2905,11 +2910,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 50796-2025 artfynd.xlsx
+++ b/artfynd/A 50796-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129806163</v>
+        <v>129806192</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615949</v>
+        <v>616113</v>
       </c>
       <c r="R2" t="n">
-        <v>6646761</v>
+        <v>6647153</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129806192</v>
+        <v>129806174</v>
       </c>
       <c r="B3" t="n">
         <v>79081</v>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616113</v>
+        <v>616053</v>
       </c>
       <c r="R3" t="n">
-        <v>6647153</v>
+        <v>6646812</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129806174</v>
+        <v>129806163</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616053</v>
+        <v>615949</v>
       </c>
       <c r="R4" t="n">
-        <v>6646812</v>
+        <v>6646761</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1071,7 +1071,7 @@
         <v>129806166</v>
       </c>
       <c r="B6" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>129806148</v>
       </c>
       <c r="B11" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129806172</v>
+        <v>129806195</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>96267</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615803</v>
+        <v>615759</v>
       </c>
       <c r="R12" t="n">
-        <v>6646576</v>
+        <v>6646541</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129806195</v>
+        <v>129806172</v>
       </c>
       <c r="B13" t="n">
-        <v>96263</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615759</v>
+        <v>615803</v>
       </c>
       <c r="R13" t="n">
-        <v>6646541</v>
+        <v>6646576</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129806175</v>
+        <v>129806161</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615799</v>
+        <v>616130</v>
       </c>
       <c r="R14" t="n">
-        <v>6646623</v>
+        <v>6647157</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1920,6 +1920,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>9. 15 st</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1946,32 +1951,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129806161</v>
+        <v>129806147</v>
       </c>
       <c r="B15" t="n">
-        <v>98774</v>
+        <v>91597</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>616130</v>
+        <v>615859</v>
       </c>
       <c r="R15" t="n">
-        <v>6647157</v>
+        <v>6646550</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2017,11 +2022,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>9. 15 st</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129806147</v>
+        <v>129806175</v>
       </c>
       <c r="B16" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615859</v>
+        <v>615799</v>
       </c>
       <c r="R16" t="n">
-        <v>6646550</v>
+        <v>6646623</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2145,32 +2145,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129806191</v>
+        <v>129806158</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>97649</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>616225</v>
+        <v>616104</v>
       </c>
       <c r="R17" t="n">
-        <v>6647187</v>
+        <v>6646974</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2242,7 +2242,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129806194</v>
+        <v>129806191</v>
       </c>
       <c r="B18" t="n">
         <v>79081</v>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616079</v>
+        <v>616225</v>
       </c>
       <c r="R18" t="n">
-        <v>6647068</v>
+        <v>6647187</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2339,32 +2339,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129806158</v>
+        <v>129806194</v>
       </c>
       <c r="B19" t="n">
-        <v>97645</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616104</v>
+        <v>616079</v>
       </c>
       <c r="R19" t="n">
-        <v>6646974</v>
+        <v>6647068</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2439,7 +2439,7 @@
         <v>129806160</v>
       </c>
       <c r="B20" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2538,32 +2538,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129806165</v>
+        <v>129806152</v>
       </c>
       <c r="B21" t="n">
-        <v>98774</v>
+        <v>57896</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>616079</v>
+        <v>615859</v>
       </c>
       <c r="R21" t="n">
-        <v>6646998</v>
+        <v>6646562</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2609,11 +2609,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2643,7 +2638,7 @@
         <v>129806170</v>
       </c>
       <c r="B22" t="n">
-        <v>105840</v>
+        <v>105844</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2737,10 +2732,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129806167</v>
+        <v>129806165</v>
       </c>
       <c r="B23" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2772,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615953</v>
+        <v>616079</v>
       </c>
       <c r="R23" t="n">
-        <v>6646752</v>
+        <v>6646998</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2812,7 +2807,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2839,32 +2834,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129806152</v>
+        <v>129806167</v>
       </c>
       <c r="B24" t="n">
-        <v>57896</v>
+        <v>98778</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2869,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615859</v>
+        <v>615953</v>
       </c>
       <c r="R24" t="n">
-        <v>6646562</v>
+        <v>6646752</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2910,6 +2905,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2939,7 +2939,7 @@
         <v>129806171</v>
       </c>
       <c r="B25" t="n">
-        <v>105840</v>
+        <v>105844</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>129806159</v>
       </c>
       <c r="B26" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>129806169</v>
       </c>
       <c r="B27" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>129806162</v>
       </c>
       <c r="B29" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3436,32 +3436,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129806146</v>
+        <v>129806155</v>
       </c>
       <c r="B30" t="n">
-        <v>91557</v>
+        <v>57733</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615873</v>
+        <v>615771</v>
       </c>
       <c r="R30" t="n">
-        <v>6646602</v>
+        <v>6646537</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3533,32 +3533,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129806155</v>
+        <v>129806168</v>
       </c>
       <c r="B31" t="n">
-        <v>57733</v>
+        <v>98778</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3568,10 +3568,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615771</v>
+        <v>615857</v>
       </c>
       <c r="R31" t="n">
-        <v>6646537</v>
+        <v>6646561</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3604,6 +3604,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3630,32 +3635,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129806168</v>
+        <v>129806146</v>
       </c>
       <c r="B32" t="n">
-        <v>98774</v>
+        <v>91561</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3665,10 +3670,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615857</v>
+        <v>615873</v>
       </c>
       <c r="R32" t="n">
-        <v>6646561</v>
+        <v>6646602</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3701,11 +3706,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 50796-2025 artfynd.xlsx
+++ b/artfynd/A 50796-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129806192</v>
+        <v>129806174</v>
       </c>
       <c r="B2" t="n">
         <v>79081</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616113</v>
+        <v>616053</v>
       </c>
       <c r="R2" t="n">
-        <v>6647153</v>
+        <v>6646812</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129806174</v>
+        <v>129806163</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616053</v>
+        <v>615949</v>
       </c>
       <c r="R3" t="n">
-        <v>6646812</v>
+        <v>6646761</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129806163</v>
+        <v>129806192</v>
       </c>
       <c r="B4" t="n">
-        <v>98778</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615949</v>
+        <v>616113</v>
       </c>
       <c r="R4" t="n">
-        <v>6646761</v>
+        <v>6647153</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1071,7 +1071,7 @@
         <v>129806166</v>
       </c>
       <c r="B6" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>129806148</v>
       </c>
       <c r="B11" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129806195</v>
+        <v>129806172</v>
       </c>
       <c r="B12" t="n">
-        <v>96267</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615759</v>
+        <v>615803</v>
       </c>
       <c r="R12" t="n">
-        <v>6646541</v>
+        <v>6646576</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129806172</v>
+        <v>129806195</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>96269</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615803</v>
+        <v>615759</v>
       </c>
       <c r="R13" t="n">
-        <v>6646576</v>
+        <v>6646541</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129806161</v>
+        <v>129806147</v>
       </c>
       <c r="B14" t="n">
-        <v>98778</v>
+        <v>91599</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>616130</v>
+        <v>615859</v>
       </c>
       <c r="R14" t="n">
-        <v>6647157</v>
+        <v>6646550</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1920,11 +1920,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>9. 15 st</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1951,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129806147</v>
+        <v>129806161</v>
       </c>
       <c r="B15" t="n">
-        <v>91597</v>
+        <v>98780</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615859</v>
+        <v>616130</v>
       </c>
       <c r="R15" t="n">
-        <v>6646550</v>
+        <v>6647157</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2022,6 +2017,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>9. 15 st</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2145,32 +2145,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129806158</v>
+        <v>129806191</v>
       </c>
       <c r="B17" t="n">
-        <v>97649</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>616104</v>
+        <v>616225</v>
       </c>
       <c r="R17" t="n">
-        <v>6646974</v>
+        <v>6647187</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2242,7 +2242,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129806191</v>
+        <v>129806194</v>
       </c>
       <c r="B18" t="n">
         <v>79081</v>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616225</v>
+        <v>616079</v>
       </c>
       <c r="R18" t="n">
-        <v>6647187</v>
+        <v>6647068</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2339,32 +2339,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129806194</v>
+        <v>129806160</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616079</v>
+        <v>616150</v>
       </c>
       <c r="R19" t="n">
-        <v>6647068</v>
+        <v>6646959</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2410,6 +2410,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>10. 30st</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2436,32 +2441,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129806160</v>
+        <v>129806158</v>
       </c>
       <c r="B20" t="n">
-        <v>98778</v>
+        <v>97651</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2471,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>616150</v>
+        <v>616104</v>
       </c>
       <c r="R20" t="n">
-        <v>6646959</v>
+        <v>6646974</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2507,11 +2512,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>10. 30st</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2635,32 +2635,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129806170</v>
+        <v>129806165</v>
       </c>
       <c r="B22" t="n">
-        <v>105844</v>
+        <v>98780</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>616130</v>
+        <v>616079</v>
       </c>
       <c r="R22" t="n">
-        <v>6647159</v>
+        <v>6646998</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2706,6 +2706,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2732,32 +2737,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129806165</v>
+        <v>129806170</v>
       </c>
       <c r="B23" t="n">
-        <v>98778</v>
+        <v>105846</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2767,10 +2772,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>616079</v>
+        <v>616130</v>
       </c>
       <c r="R23" t="n">
-        <v>6646998</v>
+        <v>6647159</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2803,11 +2808,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2837,7 +2837,7 @@
         <v>129806167</v>
       </c>
       <c r="B24" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>129806171</v>
       </c>
       <c r="B25" t="n">
-        <v>105844</v>
+        <v>105846</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>129806159</v>
       </c>
       <c r="B26" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>129806169</v>
       </c>
       <c r="B27" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>129806162</v>
       </c>
       <c r="B29" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3436,32 +3436,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129806155</v>
+        <v>129806146</v>
       </c>
       <c r="B30" t="n">
-        <v>57733</v>
+        <v>91563</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615771</v>
+        <v>615873</v>
       </c>
       <c r="R30" t="n">
-        <v>6646537</v>
+        <v>6646602</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3533,32 +3533,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129806168</v>
+        <v>129806155</v>
       </c>
       <c r="B31" t="n">
-        <v>98778</v>
+        <v>57733</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3568,10 +3568,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615857</v>
+        <v>615771</v>
       </c>
       <c r="R31" t="n">
-        <v>6646561</v>
+        <v>6646537</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3604,11 +3604,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3635,32 +3630,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129806146</v>
+        <v>129806168</v>
       </c>
       <c r="B32" t="n">
-        <v>91561</v>
+        <v>98780</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3670,10 +3665,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615873</v>
+        <v>615857</v>
       </c>
       <c r="R32" t="n">
-        <v>6646602</v>
+        <v>6646561</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3706,6 +3701,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 50796-2025 artfynd.xlsx
+++ b/artfynd/A 50796-2025 artfynd.xlsx
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129806166</v>
+        <v>129806156</v>
       </c>
       <c r="B6" t="n">
-        <v>98780</v>
+        <v>57733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616060</v>
+        <v>616164</v>
       </c>
       <c r="R6" t="n">
-        <v>6646944</v>
+        <v>6647189</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1139,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129806156</v>
+        <v>129806166</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>98780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616164</v>
+        <v>616060</v>
       </c>
       <c r="R7" t="n">
-        <v>6647189</v>
+        <v>6646944</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1241,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129806147</v>
+        <v>129806161</v>
       </c>
       <c r="B14" t="n">
-        <v>91599</v>
+        <v>98780</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615859</v>
+        <v>616130</v>
       </c>
       <c r="R14" t="n">
-        <v>6646550</v>
+        <v>6647157</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1920,6 +1920,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>9. 15 st</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1946,32 +1951,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129806161</v>
+        <v>129806175</v>
       </c>
       <c r="B15" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>616130</v>
+        <v>615799</v>
       </c>
       <c r="R15" t="n">
-        <v>6647157</v>
+        <v>6646623</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2017,11 +2022,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>9. 15 st</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129806175</v>
+        <v>129806147</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615799</v>
+        <v>615859</v>
       </c>
       <c r="R16" t="n">
-        <v>6646623</v>
+        <v>6646550</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>

--- a/artfynd/A 50796-2025 artfynd.xlsx
+++ b/artfynd/A 50796-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129806174</v>
+        <v>129806192</v>
       </c>
       <c r="B2" t="n">
         <v>79081</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616053</v>
+        <v>616113</v>
       </c>
       <c r="R2" t="n">
-        <v>6646812</v>
+        <v>6647153</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129806163</v>
+        <v>129806174</v>
       </c>
       <c r="B3" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615949</v>
+        <v>616053</v>
       </c>
       <c r="R3" t="n">
-        <v>6646761</v>
+        <v>6646812</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129806192</v>
+        <v>129806163</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616113</v>
+        <v>615949</v>
       </c>
       <c r="R4" t="n">
-        <v>6647153</v>
+        <v>6646761</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129806161</v>
+        <v>129806175</v>
       </c>
       <c r="B14" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>616130</v>
+        <v>615799</v>
       </c>
       <c r="R14" t="n">
-        <v>6647157</v>
+        <v>6646623</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1920,11 +1920,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>9. 15 st</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1951,10 +1946,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129806175</v>
+        <v>129806147</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,21 +1957,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615799</v>
+        <v>615859</v>
       </c>
       <c r="R15" t="n">
-        <v>6646623</v>
+        <v>6646550</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2048,32 +2043,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129806147</v>
+        <v>129806161</v>
       </c>
       <c r="B16" t="n">
-        <v>91599</v>
+        <v>98780</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615859</v>
+        <v>616130</v>
       </c>
       <c r="R16" t="n">
-        <v>6646550</v>
+        <v>6647157</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2119,6 +2114,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>9. 15 st</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 50796-2025 artfynd.xlsx
+++ b/artfynd/A 50796-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129806163</v>
       </c>
       <c r="B4" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129806166</v>
       </c>
       <c r="B7" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129806172</v>
+        <v>129806195</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>96279</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615803</v>
+        <v>615759</v>
       </c>
       <c r="R12" t="n">
-        <v>6646576</v>
+        <v>6646541</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129806195</v>
+        <v>129806172</v>
       </c>
       <c r="B13" t="n">
-        <v>96269</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615759</v>
+        <v>615803</v>
       </c>
       <c r="R13" t="n">
-        <v>6646541</v>
+        <v>6646576</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129806175</v>
+        <v>129806147</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615799</v>
+        <v>615859</v>
       </c>
       <c r="R14" t="n">
-        <v>6646623</v>
+        <v>6646550</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1946,10 +1946,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129806147</v>
+        <v>129806175</v>
       </c>
       <c r="B15" t="n">
-        <v>91599</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1957,21 +1957,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615859</v>
+        <v>615799</v>
       </c>
       <c r="R15" t="n">
-        <v>6646550</v>
+        <v>6646623</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2046,7 +2046,7 @@
         <v>129806161</v>
       </c>
       <c r="B16" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2145,32 +2145,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129806191</v>
+        <v>129806160</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>616225</v>
+        <v>616150</v>
       </c>
       <c r="R17" t="n">
-        <v>6647187</v>
+        <v>6646959</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2216,6 +2216,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>10. 30st</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2242,7 +2247,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129806194</v>
+        <v>129806191</v>
       </c>
       <c r="B18" t="n">
         <v>79081</v>
@@ -2277,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616079</v>
+        <v>616225</v>
       </c>
       <c r="R18" t="n">
-        <v>6647068</v>
+        <v>6647187</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2339,32 +2344,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129806160</v>
+        <v>129806194</v>
       </c>
       <c r="B19" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616150</v>
+        <v>616079</v>
       </c>
       <c r="R19" t="n">
-        <v>6646959</v>
+        <v>6647068</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2410,11 +2415,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>10. 30st</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2444,7 +2444,7 @@
         <v>129806158</v>
       </c>
       <c r="B20" t="n">
-        <v>97651</v>
+        <v>97661</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>129806165</v>
       </c>
       <c r="B22" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2737,32 +2737,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129806170</v>
+        <v>129806167</v>
       </c>
       <c r="B23" t="n">
-        <v>105846</v>
+        <v>98790</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>616130</v>
+        <v>615953</v>
       </c>
       <c r="R23" t="n">
-        <v>6647159</v>
+        <v>6646752</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2808,6 +2808,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2834,32 +2839,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129806167</v>
+        <v>129806170</v>
       </c>
       <c r="B24" t="n">
-        <v>98780</v>
+        <v>105856</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2869,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615953</v>
+        <v>616130</v>
       </c>
       <c r="R24" t="n">
-        <v>6646752</v>
+        <v>6647159</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2905,11 +2910,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2939,7 +2939,7 @@
         <v>129806171</v>
       </c>
       <c r="B25" t="n">
-        <v>105846</v>
+        <v>105856</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>129806159</v>
       </c>
       <c r="B26" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>129806169</v>
       </c>
       <c r="B27" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>129806162</v>
       </c>
       <c r="B29" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3533,32 +3533,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129806155</v>
+        <v>129806168</v>
       </c>
       <c r="B31" t="n">
-        <v>57733</v>
+        <v>98790</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3568,10 +3568,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615771</v>
+        <v>615857</v>
       </c>
       <c r="R31" t="n">
-        <v>6646537</v>
+        <v>6646561</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3604,6 +3604,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3630,32 +3635,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129806168</v>
+        <v>129806155</v>
       </c>
       <c r="B32" t="n">
-        <v>98780</v>
+        <v>57733</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3665,10 +3670,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615857</v>
+        <v>615771</v>
       </c>
       <c r="R32" t="n">
-        <v>6646561</v>
+        <v>6646537</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3701,11 +3706,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 50796-2025 artfynd.xlsx
+++ b/artfynd/A 50796-2025 artfynd.xlsx
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129806156</v>
+        <v>129806166</v>
       </c>
       <c r="B6" t="n">
-        <v>57733</v>
+        <v>98790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616164</v>
+        <v>616060</v>
       </c>
       <c r="R6" t="n">
-        <v>6647189</v>
+        <v>6646944</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1139,6 +1139,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129806166</v>
+        <v>129806156</v>
       </c>
       <c r="B7" t="n">
-        <v>98790</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616060</v>
+        <v>616164</v>
       </c>
       <c r="R7" t="n">
-        <v>6646944</v>
+        <v>6647189</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1236,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -3533,32 +3533,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129806168</v>
+        <v>129806155</v>
       </c>
       <c r="B31" t="n">
-        <v>98790</v>
+        <v>57733</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3568,10 +3568,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615857</v>
+        <v>615771</v>
       </c>
       <c r="R31" t="n">
-        <v>6646561</v>
+        <v>6646537</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3604,11 +3604,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3635,32 +3630,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129806155</v>
+        <v>129806168</v>
       </c>
       <c r="B32" t="n">
-        <v>57733</v>
+        <v>98790</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3670,10 +3665,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615771</v>
+        <v>615857</v>
       </c>
       <c r="R32" t="n">
-        <v>6646537</v>
+        <v>6646561</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3706,6 +3701,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 50796-2025 artfynd.xlsx
+++ b/artfynd/A 50796-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129806192</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129806174</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129806163</v>
       </c>
       <c r="B4" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129806149</v>
       </c>
       <c r="B5" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129806166</v>
+        <v>129806156</v>
       </c>
       <c r="B6" t="n">
-        <v>98790</v>
+        <v>57734</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616060</v>
+        <v>616164</v>
       </c>
       <c r="R6" t="n">
-        <v>6646944</v>
+        <v>6647189</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1139,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129806156</v>
+        <v>129806166</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>98794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616164</v>
+        <v>616060</v>
       </c>
       <c r="R7" t="n">
-        <v>6647189</v>
+        <v>6646944</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1241,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1270,7 +1270,7 @@
         <v>129806176</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129806173</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>129806150</v>
       </c>
       <c r="B10" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>129806148</v>
       </c>
       <c r="B11" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129806195</v>
+        <v>129806172</v>
       </c>
       <c r="B12" t="n">
-        <v>96279</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615759</v>
+        <v>615803</v>
       </c>
       <c r="R12" t="n">
-        <v>6646541</v>
+        <v>6646576</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129806172</v>
+        <v>129806195</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>96283</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615803</v>
+        <v>615759</v>
       </c>
       <c r="R13" t="n">
-        <v>6646576</v>
+        <v>6646541</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1852,7 +1852,7 @@
         <v>129806147</v>
       </c>
       <c r="B14" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>129806175</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>129806161</v>
       </c>
       <c r="B16" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2145,32 +2145,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129806160</v>
+        <v>129806194</v>
       </c>
       <c r="B17" t="n">
-        <v>98790</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>616150</v>
+        <v>616079</v>
       </c>
       <c r="R17" t="n">
-        <v>6646959</v>
+        <v>6647068</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2216,11 +2216,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>10. 30st</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2250,7 +2245,7 @@
         <v>129806191</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2344,32 +2339,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129806194</v>
+        <v>129806160</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>98794</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616079</v>
+        <v>616150</v>
       </c>
       <c r="R19" t="n">
-        <v>6647068</v>
+        <v>6646959</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2415,6 +2410,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>10. 30st</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2444,7 +2444,7 @@
         <v>129806158</v>
       </c>
       <c r="B20" t="n">
-        <v>97661</v>
+        <v>97665</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>129806152</v>
       </c>
       <c r="B21" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>129806165</v>
       </c>
       <c r="B22" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>129806167</v>
       </c>
       <c r="B23" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>129806170</v>
       </c>
       <c r="B24" t="n">
-        <v>105856</v>
+        <v>105860</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>129806171</v>
       </c>
       <c r="B25" t="n">
-        <v>105856</v>
+        <v>105860</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129806159</v>
+        <v>129806169</v>
       </c>
       <c r="B26" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>615789</v>
+        <v>615861</v>
       </c>
       <c r="R26" t="n">
-        <v>6646577</v>
+        <v>6646557</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>3. 8 st</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3135,10 +3135,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129806169</v>
+        <v>129806159</v>
       </c>
       <c r="B27" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>615861</v>
+        <v>615789</v>
       </c>
       <c r="R27" t="n">
-        <v>6646557</v>
+        <v>6646577</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3. 8 st</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3240,7 +3240,7 @@
         <v>129806157</v>
       </c>
       <c r="B28" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>129806162</v>
       </c>
       <c r="B29" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>129806146</v>
       </c>
       <c r="B30" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>129806155</v>
       </c>
       <c r="B31" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>129806168</v>
       </c>
       <c r="B32" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>129806193</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>129806151</v>
       </c>
       <c r="B34" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 50796-2025 artfynd.xlsx
+++ b/artfynd/A 50796-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129806156</v>
+        <v>129806166</v>
       </c>
       <c r="B6" t="n">
-        <v>57734</v>
+        <v>98794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616164</v>
+        <v>616060</v>
       </c>
       <c r="R6" t="n">
-        <v>6647189</v>
+        <v>6646944</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1139,6 +1139,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129806166</v>
+        <v>129806156</v>
       </c>
       <c r="B7" t="n">
-        <v>98794</v>
+        <v>57734</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616060</v>
+        <v>616164</v>
       </c>
       <c r="R7" t="n">
-        <v>6646944</v>
+        <v>6647189</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1236,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2145,32 +2145,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129806194</v>
+        <v>129806160</v>
       </c>
       <c r="B17" t="n">
-        <v>79084</v>
+        <v>98794</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>616079</v>
+        <v>616150</v>
       </c>
       <c r="R17" t="n">
-        <v>6647068</v>
+        <v>6646959</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2216,6 +2216,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>10. 30st</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2242,7 +2247,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129806191</v>
+        <v>129806194</v>
       </c>
       <c r="B18" t="n">
         <v>79084</v>
@@ -2277,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616225</v>
+        <v>616079</v>
       </c>
       <c r="R18" t="n">
-        <v>6647187</v>
+        <v>6647068</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2339,32 +2344,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129806160</v>
+        <v>129806191</v>
       </c>
       <c r="B19" t="n">
-        <v>98794</v>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616150</v>
+        <v>616225</v>
       </c>
       <c r="R19" t="n">
-        <v>6646959</v>
+        <v>6647187</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2410,11 +2415,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>10. 30st</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3033,7 +3033,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129806169</v>
+        <v>129806159</v>
       </c>
       <c r="B26" t="n">
         <v>98794</v>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>615861</v>
+        <v>615789</v>
       </c>
       <c r="R26" t="n">
-        <v>6646557</v>
+        <v>6646577</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3. 8 st</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3135,7 +3135,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129806159</v>
+        <v>129806169</v>
       </c>
       <c r="B27" t="n">
         <v>98794</v>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>615789</v>
+        <v>615861</v>
       </c>
       <c r="R27" t="n">
-        <v>6646577</v>
+        <v>6646557</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>3. 8 st</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3436,32 +3436,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129806146</v>
+        <v>129806168</v>
       </c>
       <c r="B30" t="n">
-        <v>91566</v>
+        <v>98794</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615873</v>
+        <v>615857</v>
       </c>
       <c r="R30" t="n">
-        <v>6646602</v>
+        <v>6646561</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3507,6 +3507,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3533,32 +3538,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129806155</v>
+        <v>129806146</v>
       </c>
       <c r="B31" t="n">
-        <v>57734</v>
+        <v>91566</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3568,10 +3573,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615771</v>
+        <v>615873</v>
       </c>
       <c r="R31" t="n">
-        <v>6646537</v>
+        <v>6646602</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3630,32 +3635,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129806168</v>
+        <v>129806155</v>
       </c>
       <c r="B32" t="n">
-        <v>98794</v>
+        <v>57734</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3665,10 +3670,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615857</v>
+        <v>615771</v>
       </c>
       <c r="R32" t="n">
-        <v>6646561</v>
+        <v>6646537</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3701,11 +3706,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3924,6 +3924,3706 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129976692</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>615954</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6646724</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>8 buketter</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129976700</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>616077</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6646922</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>25 buketter</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129976726</v>
+      </c>
+      <c r="B37" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>616026</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6646934</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129976698</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>616004</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6646824</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>6 buketter 1 blomstängel</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129976709</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>616081</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6647014</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129976708</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>616088</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6647065</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>2 buketter</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129976697</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>616002</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6646805</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>30buketter</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129976690</v>
+      </c>
+      <c r="B42" t="n">
+        <v>97665</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>616096</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6646883</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129976701</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>616166</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6646980</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>20 buketter</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129976694</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>615943</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6646793</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129976710</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>616105</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6646876</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>4 buketter</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129976713</v>
+      </c>
+      <c r="B46" t="n">
+        <v>105860</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>616084</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6647010</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>8 buketter</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129976689</v>
+      </c>
+      <c r="B47" t="n">
+        <v>92055</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>615951</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6646840</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129976686</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57734</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>616291</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6647141</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129976681</v>
+      </c>
+      <c r="B49" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>615950</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6646824</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129976705</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>616139</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6646955</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129976687</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57734</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>616091</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6647065</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129976685</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>616099</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6647081</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129976712</v>
+      </c>
+      <c r="B53" t="n">
+        <v>105860</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>616148</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6646963</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>8 buketter</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129976704</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>616200</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6647015</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>6 buketter</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129976695</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>616007</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6646800</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>3 buketter</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129976699</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>615998</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6646808</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>2 buketter</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129976706</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>616129</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6647133</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>30 buketter</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129976717</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>616005</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6646841</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129976716</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>615998</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6646837</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129976691</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>616007</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6646778</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>1 bukett</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129976682</v>
+      </c>
+      <c r="B61" t="n">
+        <v>91602</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>616105</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6647061</v>
+      </c>
+      <c r="S61" t="n">
+        <v>15</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129976727</v>
+      </c>
+      <c r="B62" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>615998</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6646840</v>
+      </c>
+      <c r="S62" t="n">
+        <v>15</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129976693</v>
+      </c>
+      <c r="B63" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>615940</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6646762</v>
+      </c>
+      <c r="S63" t="n">
+        <v>15</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>1 bukett</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129976684</v>
+      </c>
+      <c r="B64" t="n">
+        <v>91602</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>615950</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6646831</v>
+      </c>
+      <c r="S64" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129976702</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>616192</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6647016</v>
+      </c>
+      <c r="S65" t="n">
+        <v>15</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>4 buketter</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129976711</v>
+      </c>
+      <c r="B66" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>616085</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6647012</v>
+      </c>
+      <c r="S66" t="n">
+        <v>15</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>20 buketter</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129976688</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57734</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>615955</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6646826</v>
+      </c>
+      <c r="S67" t="n">
+        <v>15</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129976707</v>
+      </c>
+      <c r="B68" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>616125</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6647116</v>
+      </c>
+      <c r="S68" t="n">
+        <v>15</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>2 buketter</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129976715</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>616081</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6647102</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Rikligt på flera träd</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129976683</v>
+      </c>
+      <c r="B70" t="n">
+        <v>91602</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>615962</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6646716</v>
+      </c>
+      <c r="S70" t="n">
+        <v>15</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50796-2025 artfynd.xlsx
+++ b/artfynd/A 50796-2025 artfynd.xlsx
@@ -4665,45 +4665,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129976690</v>
+        <v>129976701</v>
       </c>
       <c r="B42" t="n">
-        <v>97665</v>
+        <v>98794</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>616096</v>
+        <v>616166</v>
       </c>
       <c r="R42" t="n">
-        <v>6646883</v>
+        <v>6646980</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4738,12 +4742,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>20 buketter</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4762,7 +4772,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129976701</v>
+        <v>129976694</v>
       </c>
       <c r="B43" t="n">
         <v>98794</v>
@@ -4801,10 +4811,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>616166</v>
+        <v>615943</v>
       </c>
       <c r="R43" t="n">
-        <v>6646980</v>
+        <v>6646793</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4841,7 +4851,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>20 buketter</t>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4869,49 +4879,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129976694</v>
+        <v>129976690</v>
       </c>
       <c r="B44" t="n">
-        <v>98794</v>
+        <v>97665</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>615943</v>
+        <v>616096</v>
       </c>
       <c r="R44" t="n">
-        <v>6646793</v>
+        <v>6646883</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4946,18 +4952,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5083,32 +5083,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129976713</v>
+        <v>129976689</v>
       </c>
       <c r="B46" t="n">
-        <v>105860</v>
+        <v>92055</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>616084</v>
+        <v>615951</v>
       </c>
       <c r="R46" t="n">
-        <v>6647010</v>
+        <v>6646840</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5156,18 +5156,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>8 buketter</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5186,32 +5180,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129976689</v>
+        <v>129976686</v>
       </c>
       <c r="B47" t="n">
-        <v>92055</v>
+        <v>57734</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5221,10 +5215,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>615951</v>
+        <v>616291</v>
       </c>
       <c r="R47" t="n">
-        <v>6646840</v>
+        <v>6647141</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5283,32 +5277,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129976686</v>
+        <v>129976713</v>
       </c>
       <c r="B48" t="n">
-        <v>57734</v>
+        <v>105860</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5318,10 +5312,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>616291</v>
+        <v>616084</v>
       </c>
       <c r="R48" t="n">
-        <v>6647141</v>
+        <v>6647010</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5356,12 +5350,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>8 buketter</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6610,45 +6610,49 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129976682</v>
+        <v>129976693</v>
       </c>
       <c r="B61" t="n">
-        <v>91602</v>
+        <v>98794</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>616105</v>
+        <v>615940</v>
       </c>
       <c r="R61" t="n">
-        <v>6647061</v>
+        <v>6646762</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6683,12 +6687,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>1 bukett</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6707,32 +6717,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129976727</v>
+        <v>129976682</v>
       </c>
       <c r="B62" t="n">
-        <v>5177</v>
+        <v>91602</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6742,10 +6752,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>615998</v>
+        <v>616105</v>
       </c>
       <c r="R62" t="n">
-        <v>6646840</v>
+        <v>6647061</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6804,49 +6814,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129976693</v>
+        <v>129976727</v>
       </c>
       <c r="B63" t="n">
-        <v>98794</v>
+        <v>5177</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>615940</v>
+        <v>615998</v>
       </c>
       <c r="R63" t="n">
-        <v>6646762</v>
+        <v>6646840</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6881,18 +6887,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>1 bukett</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7222,10 +7222,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129976688</v>
+        <v>129976715</v>
       </c>
       <c r="B67" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7233,21 +7233,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7257,10 +7257,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>615955</v>
+        <v>616081</v>
       </c>
       <c r="R67" t="n">
-        <v>6646826</v>
+        <v>6647102</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7295,12 +7295,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Rikligt på flera träd</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7319,49 +7325,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129976707</v>
+        <v>129976688</v>
       </c>
       <c r="B68" t="n">
-        <v>98794</v>
+        <v>57734</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>616125</v>
+        <v>615955</v>
       </c>
       <c r="R68" t="n">
-        <v>6647116</v>
+        <v>6646826</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7396,18 +7398,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>2 buketter</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7426,45 +7422,49 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129976715</v>
+        <v>129976707</v>
       </c>
       <c r="B69" t="n">
-        <v>79084</v>
+        <v>98794</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>616081</v>
+        <v>616125</v>
       </c>
       <c r="R69" t="n">
-        <v>6647102</v>
+        <v>6647116</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Rikligt på flera träd</t>
+          <t>2 buketter</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 50796-2025 artfynd.xlsx
+++ b/artfynd/A 50796-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129806192</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129806174</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129806163</v>
       </c>
       <c r="B4" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129806149</v>
       </c>
       <c r="B5" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129806166</v>
+        <v>129806156</v>
       </c>
       <c r="B6" t="n">
-        <v>98794</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616060</v>
+        <v>616164</v>
       </c>
       <c r="R6" t="n">
-        <v>6646944</v>
+        <v>6647189</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1139,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129806156</v>
+        <v>129806166</v>
       </c>
       <c r="B7" t="n">
-        <v>57734</v>
+        <v>98797</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616164</v>
+        <v>616060</v>
       </c>
       <c r="R7" t="n">
-        <v>6647189</v>
+        <v>6646944</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1241,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1270,7 +1270,7 @@
         <v>129806176</v>
       </c>
       <c r="B8" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129806173</v>
       </c>
       <c r="B9" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>129806150</v>
       </c>
       <c r="B10" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>129806148</v>
       </c>
       <c r="B11" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129806172</v>
       </c>
       <c r="B12" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>129806195</v>
       </c>
       <c r="B13" t="n">
-        <v>96283</v>
+        <v>96286</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>129806147</v>
       </c>
       <c r="B14" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>129806175</v>
       </c>
       <c r="B15" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>129806161</v>
       </c>
       <c r="B16" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2145,32 +2145,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129806160</v>
+        <v>129806194</v>
       </c>
       <c r="B17" t="n">
-        <v>98794</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>616150</v>
+        <v>616079</v>
       </c>
       <c r="R17" t="n">
-        <v>6646959</v>
+        <v>6647068</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2216,11 +2216,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>10. 30st</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2247,10 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129806194</v>
+        <v>129806191</v>
       </c>
       <c r="B18" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2282,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616079</v>
+        <v>616225</v>
       </c>
       <c r="R18" t="n">
-        <v>6647068</v>
+        <v>6647187</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2344,32 +2339,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129806191</v>
+        <v>129806160</v>
       </c>
       <c r="B19" t="n">
-        <v>79084</v>
+        <v>98797</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616225</v>
+        <v>616150</v>
       </c>
       <c r="R19" t="n">
-        <v>6647187</v>
+        <v>6646959</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2415,6 +2410,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>10. 30st</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2444,7 +2444,7 @@
         <v>129806158</v>
       </c>
       <c r="B20" t="n">
-        <v>97665</v>
+        <v>97668</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>129806152</v>
       </c>
       <c r="B21" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>129806165</v>
       </c>
       <c r="B22" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>129806167</v>
       </c>
       <c r="B23" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>129806170</v>
       </c>
       <c r="B24" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>129806171</v>
       </c>
       <c r="B25" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>129806159</v>
       </c>
       <c r="B26" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>129806169</v>
       </c>
       <c r="B27" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>129806157</v>
       </c>
       <c r="B28" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>129806162</v>
       </c>
       <c r="B29" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3436,32 +3436,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129806168</v>
+        <v>129806146</v>
       </c>
       <c r="B30" t="n">
-        <v>98794</v>
+        <v>91569</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615857</v>
+        <v>615873</v>
       </c>
       <c r="R30" t="n">
-        <v>6646561</v>
+        <v>6646602</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3507,11 +3507,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3538,32 +3533,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129806146</v>
+        <v>129806155</v>
       </c>
       <c r="B31" t="n">
-        <v>91566</v>
+        <v>57737</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3573,10 +3568,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615873</v>
+        <v>615771</v>
       </c>
       <c r="R31" t="n">
-        <v>6646602</v>
+        <v>6646537</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3635,32 +3630,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129806155</v>
+        <v>129806168</v>
       </c>
       <c r="B32" t="n">
-        <v>57734</v>
+        <v>98797</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3670,10 +3665,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615771</v>
+        <v>615857</v>
       </c>
       <c r="R32" t="n">
-        <v>6646537</v>
+        <v>6646561</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3706,6 +3701,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3735,7 +3735,7 @@
         <v>129806193</v>
       </c>
       <c r="B33" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>129806151</v>
       </c>
       <c r="B34" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>129976692</v>
       </c>
       <c r="B35" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>129976700</v>
       </c>
       <c r="B36" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>129976698</v>
       </c>
       <c r="B38" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>129976709</v>
       </c>
       <c r="B39" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>129976708</v>
       </c>
       <c r="B40" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>129976697</v>
       </c>
       <c r="B41" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>129976701</v>
       </c>
       <c r="B42" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>129976694</v>
       </c>
       <c r="B43" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>129976690</v>
       </c>
       <c r="B44" t="n">
-        <v>97665</v>
+        <v>97668</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>129976710</v>
       </c>
       <c r="B45" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5083,32 +5083,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129976689</v>
+        <v>129976713</v>
       </c>
       <c r="B46" t="n">
-        <v>92055</v>
+        <v>105863</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>615951</v>
+        <v>616084</v>
       </c>
       <c r="R46" t="n">
-        <v>6646840</v>
+        <v>6647010</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5156,12 +5156,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>8 buketter</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5180,32 +5186,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129976686</v>
+        <v>129976689</v>
       </c>
       <c r="B47" t="n">
-        <v>57734</v>
+        <v>92058</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5215,10 +5221,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>616291</v>
+        <v>615951</v>
       </c>
       <c r="R47" t="n">
-        <v>6647141</v>
+        <v>6646840</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5277,32 +5283,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129976713</v>
+        <v>129976686</v>
       </c>
       <c r="B48" t="n">
-        <v>105860</v>
+        <v>57737</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5312,10 +5318,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>616084</v>
+        <v>616291</v>
       </c>
       <c r="R48" t="n">
-        <v>6647010</v>
+        <v>6647141</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5350,18 +5356,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>8 buketter</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5480,7 +5480,7 @@
         <v>129976705</v>
       </c>
       <c r="B50" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>129976687</v>
       </c>
       <c r="B51" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>129976685</v>
       </c>
       <c r="B52" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>129976712</v>
       </c>
       <c r="B53" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>129976704</v>
       </c>
       <c r="B54" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>129976695</v>
       </c>
       <c r="B55" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>129976699</v>
       </c>
       <c r="B56" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>129976706</v>
       </c>
       <c r="B57" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         <v>129976717</v>
       </c>
       <c r="B58" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>129976716</v>
       </c>
       <c r="B59" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>129976691</v>
       </c>
       <c r="B60" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6610,49 +6610,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129976693</v>
+        <v>129976727</v>
       </c>
       <c r="B61" t="n">
-        <v>98794</v>
+        <v>5177</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>615940</v>
+        <v>615998</v>
       </c>
       <c r="R61" t="n">
-        <v>6646762</v>
+        <v>6646840</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6687,18 +6683,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>1 bukett</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6720,7 +6710,7 @@
         <v>129976682</v>
       </c>
       <c r="B62" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6814,45 +6804,49 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129976727</v>
+        <v>129976693</v>
       </c>
       <c r="B63" t="n">
-        <v>5177</v>
+        <v>98797</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>615998</v>
+        <v>615940</v>
       </c>
       <c r="R63" t="n">
-        <v>6646840</v>
+        <v>6646762</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6887,12 +6881,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>1 bukett</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6914,7 +6914,7 @@
         <v>129976684</v>
       </c>
       <c r="B64" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>129976702</v>
       </c>
       <c r="B65" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>129976711</v>
       </c>
       <c r="B66" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7222,10 +7222,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129976715</v>
+        <v>129976688</v>
       </c>
       <c r="B67" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7233,21 +7233,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7257,10 +7257,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>616081</v>
+        <v>615955</v>
       </c>
       <c r="R67" t="n">
-        <v>6647102</v>
+        <v>6646826</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7295,18 +7295,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt på flera träd</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7325,10 +7319,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129976688</v>
+        <v>129976715</v>
       </c>
       <c r="B68" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7336,21 +7330,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7360,10 +7354,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>615955</v>
+        <v>616081</v>
       </c>
       <c r="R68" t="n">
-        <v>6646826</v>
+        <v>6647102</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7398,12 +7392,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt på flera träd</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7425,7 +7425,7 @@
         <v>129976707</v>
       </c>
       <c r="B69" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>129976683</v>
       </c>
       <c r="B70" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 50796-2025 artfynd.xlsx
+++ b/artfynd/A 50796-2025 artfynd.xlsx
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129806156</v>
+        <v>129806166</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>98797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616164</v>
+        <v>616060</v>
       </c>
       <c r="R6" t="n">
-        <v>6647189</v>
+        <v>6646944</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1139,6 +1139,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129806166</v>
+        <v>129806156</v>
       </c>
       <c r="B7" t="n">
-        <v>98797</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616060</v>
+        <v>616164</v>
       </c>
       <c r="R7" t="n">
-        <v>6646944</v>
+        <v>6647189</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1236,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129806147</v>
+        <v>129806161</v>
       </c>
       <c r="B14" t="n">
-        <v>91605</v>
+        <v>98797</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615859</v>
+        <v>616130</v>
       </c>
       <c r="R14" t="n">
-        <v>6646550</v>
+        <v>6647157</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1920,6 +1920,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>9. 15 st</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1946,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129806175</v>
+        <v>129806147</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>91605</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1957,21 +1962,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615799</v>
+        <v>615859</v>
       </c>
       <c r="R15" t="n">
-        <v>6646623</v>
+        <v>6646550</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2043,32 +2048,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129806161</v>
+        <v>129806175</v>
       </c>
       <c r="B16" t="n">
-        <v>98797</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>616130</v>
+        <v>615799</v>
       </c>
       <c r="R16" t="n">
-        <v>6647157</v>
+        <v>6646623</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2114,11 +2119,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>9. 15 st</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -5681,32 +5681,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129976685</v>
+        <v>129976712</v>
       </c>
       <c r="B52" t="n">
-        <v>57898</v>
+        <v>105863</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5716,10 +5716,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>616099</v>
+        <v>616148</v>
       </c>
       <c r="R52" t="n">
-        <v>6647081</v>
+        <v>6646963</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5754,12 +5754,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>8 buketter</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5778,32 +5784,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129976712</v>
+        <v>129976685</v>
       </c>
       <c r="B53" t="n">
-        <v>105863</v>
+        <v>57898</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5813,10 +5819,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>616148</v>
+        <v>616099</v>
       </c>
       <c r="R53" t="n">
-        <v>6646963</v>
+        <v>6647081</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5851,18 +5857,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>8 buketter</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50796-2025 artfynd.xlsx
+++ b/artfynd/A 50796-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129806192</v>
+        <v>129806163</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>98797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616113</v>
+        <v>615949</v>
       </c>
       <c r="R2" t="n">
-        <v>6647153</v>
+        <v>6646761</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129806174</v>
+        <v>129806192</v>
       </c>
       <c r="B3" t="n">
         <v>79087</v>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616053</v>
+        <v>616113</v>
       </c>
       <c r="R3" t="n">
-        <v>6646812</v>
+        <v>6647153</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129806163</v>
+        <v>129806174</v>
       </c>
       <c r="B4" t="n">
-        <v>98797</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615949</v>
+        <v>616053</v>
       </c>
       <c r="R4" t="n">
-        <v>6646761</v>
+        <v>6646812</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129806166</v>
+        <v>129806156</v>
       </c>
       <c r="B6" t="n">
-        <v>98797</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616060</v>
+        <v>616164</v>
       </c>
       <c r="R6" t="n">
-        <v>6646944</v>
+        <v>6647189</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1139,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129806156</v>
+        <v>129806166</v>
       </c>
       <c r="B7" t="n">
-        <v>57737</v>
+        <v>98797</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616164</v>
+        <v>616060</v>
       </c>
       <c r="R7" t="n">
-        <v>6647189</v>
+        <v>6646944</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1241,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2145,32 +2145,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129806194</v>
+        <v>129806158</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>97668</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>616079</v>
+        <v>616104</v>
       </c>
       <c r="R17" t="n">
-        <v>6647068</v>
+        <v>6646974</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2242,32 +2242,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129806191</v>
+        <v>129806160</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>98797</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616225</v>
+        <v>616150</v>
       </c>
       <c r="R18" t="n">
-        <v>6647187</v>
+        <v>6646959</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2313,6 +2313,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>10. 30st</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2339,32 +2344,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129806160</v>
+        <v>129806194</v>
       </c>
       <c r="B19" t="n">
-        <v>98797</v>
+        <v>79087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616150</v>
+        <v>616079</v>
       </c>
       <c r="R19" t="n">
-        <v>6646959</v>
+        <v>6647068</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2410,11 +2415,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>10. 30st</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2441,32 +2441,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129806158</v>
+        <v>129806191</v>
       </c>
       <c r="B20" t="n">
-        <v>97668</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>616104</v>
+        <v>616225</v>
       </c>
       <c r="R20" t="n">
-        <v>6646974</v>
+        <v>6647187</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -5681,32 +5681,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129976712</v>
+        <v>129976685</v>
       </c>
       <c r="B52" t="n">
-        <v>105863</v>
+        <v>57898</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5716,10 +5716,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>616148</v>
+        <v>616099</v>
       </c>
       <c r="R52" t="n">
-        <v>6646963</v>
+        <v>6647081</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5754,18 +5754,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>8 buketter</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5784,32 +5778,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129976685</v>
+        <v>129976712</v>
       </c>
       <c r="B53" t="n">
-        <v>57898</v>
+        <v>105863</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5819,10 +5813,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>616099</v>
+        <v>616148</v>
       </c>
       <c r="R53" t="n">
-        <v>6647081</v>
+        <v>6646963</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5857,12 +5851,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>8 buketter</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6707,45 +6707,49 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129976682</v>
+        <v>129976693</v>
       </c>
       <c r="B62" t="n">
-        <v>91605</v>
+        <v>98797</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>616105</v>
+        <v>615940</v>
       </c>
       <c r="R62" t="n">
-        <v>6647061</v>
+        <v>6646762</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6780,12 +6784,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>1 bukett</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6804,49 +6814,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129976693</v>
+        <v>129976682</v>
       </c>
       <c r="B63" t="n">
-        <v>98797</v>
+        <v>91605</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>615940</v>
+        <v>616105</v>
       </c>
       <c r="R63" t="n">
-        <v>6646762</v>
+        <v>6647061</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6881,18 +6887,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>1 bukett</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7222,45 +7222,49 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129976688</v>
+        <v>129976707</v>
       </c>
       <c r="B67" t="n">
-        <v>57737</v>
+        <v>98797</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>615955</v>
+        <v>616125</v>
       </c>
       <c r="R67" t="n">
-        <v>6646826</v>
+        <v>6647116</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7295,12 +7299,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>2 buketter</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7422,49 +7432,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129976707</v>
+        <v>129976688</v>
       </c>
       <c r="B69" t="n">
-        <v>98797</v>
+        <v>57737</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>616125</v>
+        <v>615955</v>
       </c>
       <c r="R69" t="n">
-        <v>6647116</v>
+        <v>6646826</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7499,18 +7505,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>2 buketter</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50796-2025 artfynd.xlsx
+++ b/artfynd/A 50796-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129806163</v>
+        <v>129806174</v>
       </c>
       <c r="B2" t="n">
-        <v>98797</v>
+        <v>79088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615949</v>
+        <v>616053</v>
       </c>
       <c r="R2" t="n">
-        <v>6646761</v>
+        <v>6646812</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,7 +775,7 @@
         <v>129806192</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129806174</v>
+        <v>129806163</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>98798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616053</v>
+        <v>615949</v>
       </c>
       <c r="R4" t="n">
-        <v>6646812</v>
+        <v>6646761</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1168,7 +1168,7 @@
         <v>129806166</v>
       </c>
       <c r="B7" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129806176</v>
+        <v>129806173</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616099</v>
+        <v>616036</v>
       </c>
       <c r="R8" t="n">
-        <v>6647122</v>
+        <v>6646801</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129806173</v>
+        <v>129806176</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616036</v>
+        <v>616099</v>
       </c>
       <c r="R9" t="n">
-        <v>6646801</v>
+        <v>6647122</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1561,7 +1561,7 @@
         <v>129806148</v>
       </c>
       <c r="B11" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129806172</v>
+        <v>129806195</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>96287</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615803</v>
+        <v>615759</v>
       </c>
       <c r="R12" t="n">
-        <v>6646576</v>
+        <v>6646541</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129806195</v>
+        <v>129806172</v>
       </c>
       <c r="B13" t="n">
-        <v>96286</v>
+        <v>79088</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615759</v>
+        <v>615803</v>
       </c>
       <c r="R13" t="n">
-        <v>6646541</v>
+        <v>6646576</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129806161</v>
+        <v>129806175</v>
       </c>
       <c r="B14" t="n">
-        <v>98797</v>
+        <v>79088</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>616130</v>
+        <v>615799</v>
       </c>
       <c r="R14" t="n">
-        <v>6647157</v>
+        <v>6646623</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1920,11 +1920,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>9. 15 st</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1951,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129806147</v>
+        <v>129806161</v>
       </c>
       <c r="B15" t="n">
-        <v>91605</v>
+        <v>98798</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615859</v>
+        <v>616130</v>
       </c>
       <c r="R15" t="n">
-        <v>6646550</v>
+        <v>6647157</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2022,6 +2017,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>9. 15 st</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129806175</v>
+        <v>129806147</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>91606</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615799</v>
+        <v>615859</v>
       </c>
       <c r="R16" t="n">
-        <v>6646623</v>
+        <v>6646550</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2148,7 +2148,7 @@
         <v>129806158</v>
       </c>
       <c r="B17" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>129806160</v>
       </c>
       <c r="B18" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129806194</v>
+        <v>129806191</v>
       </c>
       <c r="B19" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616079</v>
+        <v>616225</v>
       </c>
       <c r="R19" t="n">
-        <v>6647068</v>
+        <v>6647187</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129806191</v>
+        <v>129806194</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>616225</v>
+        <v>616079</v>
       </c>
       <c r="R20" t="n">
-        <v>6647187</v>
+        <v>6647068</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2635,32 +2635,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129806165</v>
+        <v>129806170</v>
       </c>
       <c r="B22" t="n">
-        <v>98797</v>
+        <v>105864</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>616079</v>
+        <v>616130</v>
       </c>
       <c r="R22" t="n">
-        <v>6646998</v>
+        <v>6647159</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2706,11 +2706,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2737,10 +2732,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129806167</v>
+        <v>129806165</v>
       </c>
       <c r="B23" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2772,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615953</v>
+        <v>616079</v>
       </c>
       <c r="R23" t="n">
-        <v>6646752</v>
+        <v>6646998</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2812,7 +2807,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2839,32 +2834,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129806170</v>
+        <v>129806167</v>
       </c>
       <c r="B24" t="n">
-        <v>105863</v>
+        <v>98798</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2869,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>616130</v>
+        <v>615953</v>
       </c>
       <c r="R24" t="n">
-        <v>6647159</v>
+        <v>6646752</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2910,6 +2905,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2939,7 +2939,7 @@
         <v>129806171</v>
       </c>
       <c r="B25" t="n">
-        <v>105863</v>
+        <v>105864</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>129806159</v>
       </c>
       <c r="B26" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>129806169</v>
       </c>
       <c r="B27" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>129806162</v>
       </c>
       <c r="B29" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3436,32 +3436,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129806146</v>
+        <v>129806155</v>
       </c>
       <c r="B30" t="n">
-        <v>91569</v>
+        <v>57737</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615873</v>
+        <v>615771</v>
       </c>
       <c r="R30" t="n">
-        <v>6646602</v>
+        <v>6646537</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3533,32 +3533,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129806155</v>
+        <v>129806146</v>
       </c>
       <c r="B31" t="n">
-        <v>57737</v>
+        <v>91570</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3568,10 +3568,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615771</v>
+        <v>615873</v>
       </c>
       <c r="R31" t="n">
-        <v>6646537</v>
+        <v>6646602</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3633,7 +3633,7 @@
         <v>129806168</v>
       </c>
       <c r="B32" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>129806193</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>129976692</v>
       </c>
       <c r="B35" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>129976700</v>
       </c>
       <c r="B36" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>129976698</v>
       </c>
       <c r="B38" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>129976709</v>
       </c>
       <c r="B39" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4451,49 +4451,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129976708</v>
+        <v>129976690</v>
       </c>
       <c r="B40" t="n">
-        <v>98797</v>
+        <v>97669</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>616088</v>
+        <v>616096</v>
       </c>
       <c r="R40" t="n">
-        <v>6647065</v>
+        <v>6646883</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4528,18 +4524,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>2 buketter</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4558,10 +4548,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129976697</v>
+        <v>129976708</v>
       </c>
       <c r="B41" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4597,10 +4587,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>616002</v>
+        <v>616088</v>
       </c>
       <c r="R41" t="n">
-        <v>6646805</v>
+        <v>6647065</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4637,7 +4627,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>30buketter</t>
+          <t>2 buketter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4665,10 +4655,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129976701</v>
+        <v>129976697</v>
       </c>
       <c r="B42" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4704,10 +4694,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>616166</v>
+        <v>616002</v>
       </c>
       <c r="R42" t="n">
-        <v>6646980</v>
+        <v>6646805</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4744,7 +4734,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>20 buketter</t>
+          <t>30buketter</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4772,10 +4762,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129976694</v>
+        <v>129976701</v>
       </c>
       <c r="B43" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4811,10 +4801,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>615943</v>
+        <v>616166</v>
       </c>
       <c r="R43" t="n">
-        <v>6646793</v>
+        <v>6646980</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4851,7 +4841,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>10 buketter</t>
+          <t>20 buketter</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4879,45 +4869,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129976690</v>
+        <v>129976694</v>
       </c>
       <c r="B44" t="n">
-        <v>97668</v>
+        <v>98798</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>616096</v>
+        <v>615943</v>
       </c>
       <c r="R44" t="n">
-        <v>6646883</v>
+        <v>6646793</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4952,12 +4946,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4979,7 +4979,7 @@
         <v>129976710</v>
       </c>
       <c r="B45" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5083,32 +5083,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129976713</v>
+        <v>129976689</v>
       </c>
       <c r="B46" t="n">
-        <v>105863</v>
+        <v>92059</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>616084</v>
+        <v>615951</v>
       </c>
       <c r="R46" t="n">
-        <v>6647010</v>
+        <v>6646840</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5156,18 +5156,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>8 buketter</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5186,32 +5180,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129976689</v>
+        <v>129976686</v>
       </c>
       <c r="B47" t="n">
-        <v>92058</v>
+        <v>57737</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5221,10 +5215,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>615951</v>
+        <v>616291</v>
       </c>
       <c r="R47" t="n">
-        <v>6646840</v>
+        <v>6647141</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5283,32 +5277,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129976686</v>
+        <v>129976713</v>
       </c>
       <c r="B48" t="n">
-        <v>57737</v>
+        <v>105864</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5318,10 +5312,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>616291</v>
+        <v>616084</v>
       </c>
       <c r="R48" t="n">
-        <v>6647141</v>
+        <v>6647010</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5356,12 +5350,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>8 buketter</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5480,7 +5480,7 @@
         <v>129976705</v>
       </c>
       <c r="B50" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>129976712</v>
       </c>
       <c r="B53" t="n">
-        <v>105863</v>
+        <v>105864</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>129976704</v>
       </c>
       <c r="B54" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>129976695</v>
       </c>
       <c r="B55" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>129976699</v>
       </c>
       <c r="B56" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>129976706</v>
       </c>
       <c r="B57" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         <v>129976717</v>
       </c>
       <c r="B58" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6406,45 +6406,49 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129976716</v>
+        <v>129976691</v>
       </c>
       <c r="B59" t="n">
-        <v>79087</v>
+        <v>98798</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>615998</v>
+        <v>616007</v>
       </c>
       <c r="R59" t="n">
-        <v>6646837</v>
+        <v>6646778</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6479,12 +6483,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>1 bukett</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6503,49 +6513,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129976691</v>
+        <v>129976716</v>
       </c>
       <c r="B60" t="n">
-        <v>98797</v>
+        <v>79088</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>616007</v>
+        <v>615998</v>
       </c>
       <c r="R60" t="n">
-        <v>6646778</v>
+        <v>6646837</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6580,18 +6586,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>1 bukett</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6610,32 +6610,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129976727</v>
+        <v>129976682</v>
       </c>
       <c r="B61" t="n">
-        <v>5177</v>
+        <v>91606</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6645,10 +6645,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>615998</v>
+        <v>616105</v>
       </c>
       <c r="R61" t="n">
-        <v>6646840</v>
+        <v>6647061</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6707,49 +6707,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129976693</v>
+        <v>129976727</v>
       </c>
       <c r="B62" t="n">
-        <v>98797</v>
+        <v>5177</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>615940</v>
+        <v>615998</v>
       </c>
       <c r="R62" t="n">
-        <v>6646762</v>
+        <v>6646840</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6784,18 +6780,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>1 bukett</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6814,45 +6804,49 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129976682</v>
+        <v>129976693</v>
       </c>
       <c r="B63" t="n">
-        <v>91605</v>
+        <v>98798</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>616105</v>
+        <v>615940</v>
       </c>
       <c r="R63" t="n">
-        <v>6647061</v>
+        <v>6646762</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6887,12 +6881,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>1 bukett</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6914,7 +6914,7 @@
         <v>129976684</v>
       </c>
       <c r="B64" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>129976702</v>
       </c>
       <c r="B65" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>129976711</v>
       </c>
       <c r="B66" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7222,49 +7222,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129976707</v>
+        <v>129976715</v>
       </c>
       <c r="B67" t="n">
-        <v>98797</v>
+        <v>79088</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>616125</v>
+        <v>616081</v>
       </c>
       <c r="R67" t="n">
-        <v>6647116</v>
+        <v>6647102</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7301,7 +7297,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>2 buketter</t>
+          <t>Rikligt på flera träd</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7329,10 +7325,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129976715</v>
+        <v>129976688</v>
       </c>
       <c r="B68" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7340,21 +7336,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7364,10 +7360,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>616081</v>
+        <v>615955</v>
       </c>
       <c r="R68" t="n">
-        <v>6647102</v>
+        <v>6646826</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7402,18 +7398,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt på flera träd</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7432,45 +7422,49 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129976688</v>
+        <v>129976707</v>
       </c>
       <c r="B69" t="n">
-        <v>57737</v>
+        <v>98798</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>615955</v>
+        <v>616125</v>
       </c>
       <c r="R69" t="n">
-        <v>6646826</v>
+        <v>6647116</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7505,12 +7499,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>2 buketter</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7532,7 +7532,7 @@
         <v>129976683</v>
       </c>
       <c r="B70" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 50796-2025 artfynd.xlsx
+++ b/artfynd/A 50796-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129806174</v>
+        <v>129806163</v>
       </c>
       <c r="B2" t="n">
-        <v>79088</v>
+        <v>98798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616053</v>
+        <v>615949</v>
       </c>
       <c r="R2" t="n">
-        <v>6646812</v>
+        <v>6646761</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129806192</v>
+        <v>129806174</v>
       </c>
       <c r="B3" t="n">
         <v>79088</v>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616113</v>
+        <v>616053</v>
       </c>
       <c r="R3" t="n">
-        <v>6647153</v>
+        <v>6646812</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129806163</v>
+        <v>129806192</v>
       </c>
       <c r="B4" t="n">
-        <v>98798</v>
+        <v>79088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615949</v>
+        <v>616113</v>
       </c>
       <c r="R4" t="n">
-        <v>6646761</v>
+        <v>6647153</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129806156</v>
+        <v>129806166</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>98798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616164</v>
+        <v>616060</v>
       </c>
       <c r="R6" t="n">
-        <v>6647189</v>
+        <v>6646944</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1139,6 +1139,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129806166</v>
+        <v>129806156</v>
       </c>
       <c r="B7" t="n">
-        <v>98798</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616060</v>
+        <v>616164</v>
       </c>
       <c r="R7" t="n">
-        <v>6646944</v>
+        <v>6647189</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1236,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1946,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129806161</v>
+        <v>129806147</v>
       </c>
       <c r="B15" t="n">
-        <v>98798</v>
+        <v>91606</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>616130</v>
+        <v>615859</v>
       </c>
       <c r="R15" t="n">
-        <v>6647157</v>
+        <v>6646550</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2017,11 +2017,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>9. 15 st</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2048,32 +2043,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129806147</v>
+        <v>129806161</v>
       </c>
       <c r="B16" t="n">
-        <v>91606</v>
+        <v>98798</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615859</v>
+        <v>616130</v>
       </c>
       <c r="R16" t="n">
-        <v>6646550</v>
+        <v>6647157</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2119,6 +2114,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>9. 15 st</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2344,7 +2344,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129806191</v>
+        <v>129806194</v>
       </c>
       <c r="B19" t="n">
         <v>79088</v>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616225</v>
+        <v>616079</v>
       </c>
       <c r="R19" t="n">
-        <v>6647187</v>
+        <v>6647068</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2441,7 +2441,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129806194</v>
+        <v>129806191</v>
       </c>
       <c r="B20" t="n">
         <v>79088</v>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>616079</v>
+        <v>616225</v>
       </c>
       <c r="R20" t="n">
-        <v>6647068</v>
+        <v>6647187</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -3436,32 +3436,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129806155</v>
+        <v>129806146</v>
       </c>
       <c r="B30" t="n">
-        <v>57737</v>
+        <v>91570</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615771</v>
+        <v>615873</v>
       </c>
       <c r="R30" t="n">
-        <v>6646537</v>
+        <v>6646602</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3533,32 +3533,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129806146</v>
+        <v>129806155</v>
       </c>
       <c r="B31" t="n">
-        <v>91570</v>
+        <v>57737</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3568,10 +3568,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615873</v>
+        <v>615771</v>
       </c>
       <c r="R31" t="n">
-        <v>6646602</v>
+        <v>6646537</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4451,45 +4451,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129976690</v>
+        <v>129976708</v>
       </c>
       <c r="B40" t="n">
-        <v>97669</v>
+        <v>98798</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>616096</v>
+        <v>616088</v>
       </c>
       <c r="R40" t="n">
-        <v>6646883</v>
+        <v>6647065</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4524,12 +4528,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>2 buketter</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4548,7 +4558,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129976708</v>
+        <v>129976697</v>
       </c>
       <c r="B41" t="n">
         <v>98798</v>
@@ -4587,10 +4597,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>616088</v>
+        <v>616002</v>
       </c>
       <c r="R41" t="n">
-        <v>6647065</v>
+        <v>6646805</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4627,7 +4637,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>2 buketter</t>
+          <t>30buketter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4655,7 +4665,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129976697</v>
+        <v>129976701</v>
       </c>
       <c r="B42" t="n">
         <v>98798</v>
@@ -4694,10 +4704,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>616002</v>
+        <v>616166</v>
       </c>
       <c r="R42" t="n">
-        <v>6646805</v>
+        <v>6646980</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4734,7 +4744,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>30buketter</t>
+          <t>20 buketter</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4762,7 +4772,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129976701</v>
+        <v>129976694</v>
       </c>
       <c r="B43" t="n">
         <v>98798</v>
@@ -4801,10 +4811,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>616166</v>
+        <v>615943</v>
       </c>
       <c r="R43" t="n">
-        <v>6646980</v>
+        <v>6646793</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4841,7 +4851,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>20 buketter</t>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4869,49 +4879,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129976694</v>
+        <v>129976690</v>
       </c>
       <c r="B44" t="n">
-        <v>98798</v>
+        <v>97669</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>615943</v>
+        <v>616096</v>
       </c>
       <c r="R44" t="n">
-        <v>6646793</v>
+        <v>6646883</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4946,18 +4952,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6406,49 +6406,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129976691</v>
+        <v>129976716</v>
       </c>
       <c r="B59" t="n">
-        <v>98798</v>
+        <v>79088</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>616007</v>
+        <v>615998</v>
       </c>
       <c r="R59" t="n">
-        <v>6646778</v>
+        <v>6646837</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6483,18 +6479,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>1 bukett</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6513,45 +6503,49 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129976716</v>
+        <v>129976691</v>
       </c>
       <c r="B60" t="n">
-        <v>79088</v>
+        <v>98798</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>615998</v>
+        <v>616007</v>
       </c>
       <c r="R60" t="n">
-        <v>6646837</v>
+        <v>6646778</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6586,12 +6580,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>1 bukett</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6610,32 +6610,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129976682</v>
+        <v>129976727</v>
       </c>
       <c r="B61" t="n">
-        <v>91606</v>
+        <v>5177</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6645,10 +6645,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>616105</v>
+        <v>615998</v>
       </c>
       <c r="R61" t="n">
-        <v>6647061</v>
+        <v>6646840</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6707,32 +6707,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129976727</v>
+        <v>129976682</v>
       </c>
       <c r="B62" t="n">
-        <v>5177</v>
+        <v>91606</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>615998</v>
+        <v>616105</v>
       </c>
       <c r="R62" t="n">
-        <v>6646840</v>
+        <v>6647061</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>

--- a/artfynd/A 50796-2025 artfynd.xlsx
+++ b/artfynd/A 50796-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129806163</v>
+        <v>129806174</v>
       </c>
       <c r="B2" t="n">
-        <v>98798</v>
+        <v>79088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615949</v>
+        <v>616053</v>
       </c>
       <c r="R2" t="n">
-        <v>6646761</v>
+        <v>6646812</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129806174</v>
+        <v>129806192</v>
       </c>
       <c r="B3" t="n">
         <v>79088</v>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616053</v>
+        <v>616113</v>
       </c>
       <c r="R3" t="n">
-        <v>6646812</v>
+        <v>6647153</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129806192</v>
+        <v>129806163</v>
       </c>
       <c r="B4" t="n">
-        <v>79088</v>
+        <v>98798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616113</v>
+        <v>615949</v>
       </c>
       <c r="R4" t="n">
-        <v>6647153</v>
+        <v>6646761</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129806166</v>
+        <v>129806156</v>
       </c>
       <c r="B6" t="n">
-        <v>98798</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616060</v>
+        <v>616164</v>
       </c>
       <c r="R6" t="n">
-        <v>6646944</v>
+        <v>6647189</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1139,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129806156</v>
+        <v>129806166</v>
       </c>
       <c r="B7" t="n">
-        <v>57737</v>
+        <v>98798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616164</v>
+        <v>616060</v>
       </c>
       <c r="R7" t="n">
-        <v>6647189</v>
+        <v>6646944</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1241,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1946,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129806147</v>
+        <v>129806161</v>
       </c>
       <c r="B15" t="n">
-        <v>91606</v>
+        <v>98798</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615859</v>
+        <v>616130</v>
       </c>
       <c r="R15" t="n">
-        <v>6646550</v>
+        <v>6647157</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2017,6 +2017,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>9. 15 st</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2043,32 +2048,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129806161</v>
+        <v>129806147</v>
       </c>
       <c r="B16" t="n">
-        <v>98798</v>
+        <v>91606</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>616130</v>
+        <v>615859</v>
       </c>
       <c r="R16" t="n">
-        <v>6647157</v>
+        <v>6646550</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2114,11 +2119,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>9. 15 st</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2344,7 +2344,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129806194</v>
+        <v>129806191</v>
       </c>
       <c r="B19" t="n">
         <v>79088</v>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616079</v>
+        <v>616225</v>
       </c>
       <c r="R19" t="n">
-        <v>6647068</v>
+        <v>6647187</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2441,7 +2441,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129806191</v>
+        <v>129806194</v>
       </c>
       <c r="B20" t="n">
         <v>79088</v>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>616225</v>
+        <v>616079</v>
       </c>
       <c r="R20" t="n">
-        <v>6647187</v>
+        <v>6647068</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2538,32 +2538,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129806152</v>
+        <v>129806170</v>
       </c>
       <c r="B21" t="n">
-        <v>57898</v>
+        <v>105864</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615859</v>
+        <v>616130</v>
       </c>
       <c r="R21" t="n">
-        <v>6646562</v>
+        <v>6647159</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2635,32 +2635,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129806170</v>
+        <v>129806165</v>
       </c>
       <c r="B22" t="n">
-        <v>105864</v>
+        <v>98798</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>616130</v>
+        <v>616079</v>
       </c>
       <c r="R22" t="n">
-        <v>6647159</v>
+        <v>6646998</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2706,6 +2706,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2732,7 +2737,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129806165</v>
+        <v>129806167</v>
       </c>
       <c r="B23" t="n">
         <v>98798</v>
@@ -2767,10 +2772,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>616079</v>
+        <v>615953</v>
       </c>
       <c r="R23" t="n">
-        <v>6646998</v>
+        <v>6646752</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2807,7 +2812,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2834,32 +2839,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129806167</v>
+        <v>129806152</v>
       </c>
       <c r="B24" t="n">
-        <v>98798</v>
+        <v>57898</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2869,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615953</v>
+        <v>615859</v>
       </c>
       <c r="R24" t="n">
-        <v>6646752</v>
+        <v>6646562</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2905,11 +2910,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3436,32 +3436,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129806146</v>
+        <v>129806155</v>
       </c>
       <c r="B30" t="n">
-        <v>91570</v>
+        <v>57737</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615873</v>
+        <v>615771</v>
       </c>
       <c r="R30" t="n">
-        <v>6646602</v>
+        <v>6646537</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3533,32 +3533,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129806155</v>
+        <v>129806146</v>
       </c>
       <c r="B31" t="n">
-        <v>57737</v>
+        <v>91570</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3568,10 +3568,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615771</v>
+        <v>615873</v>
       </c>
       <c r="R31" t="n">
-        <v>6646537</v>
+        <v>6646602</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4451,49 +4451,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129976708</v>
+        <v>129976690</v>
       </c>
       <c r="B40" t="n">
-        <v>98798</v>
+        <v>97669</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>616088</v>
+        <v>616096</v>
       </c>
       <c r="R40" t="n">
-        <v>6647065</v>
+        <v>6646883</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4528,18 +4524,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>2 buketter</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4558,7 +4548,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129976697</v>
+        <v>129976708</v>
       </c>
       <c r="B41" t="n">
         <v>98798</v>
@@ -4597,10 +4587,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>616002</v>
+        <v>616088</v>
       </c>
       <c r="R41" t="n">
-        <v>6646805</v>
+        <v>6647065</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4637,7 +4627,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>30buketter</t>
+          <t>2 buketter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4665,7 +4655,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129976701</v>
+        <v>129976697</v>
       </c>
       <c r="B42" t="n">
         <v>98798</v>
@@ -4704,10 +4694,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>616166</v>
+        <v>616002</v>
       </c>
       <c r="R42" t="n">
-        <v>6646980</v>
+        <v>6646805</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4744,7 +4734,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>20 buketter</t>
+          <t>30buketter</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4772,7 +4762,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129976694</v>
+        <v>129976701</v>
       </c>
       <c r="B43" t="n">
         <v>98798</v>
@@ -4811,10 +4801,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>615943</v>
+        <v>616166</v>
       </c>
       <c r="R43" t="n">
-        <v>6646793</v>
+        <v>6646980</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4851,7 +4841,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>10 buketter</t>
+          <t>20 buketter</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4879,45 +4869,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129976690</v>
+        <v>129976694</v>
       </c>
       <c r="B44" t="n">
-        <v>97669</v>
+        <v>98798</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>616096</v>
+        <v>615943</v>
       </c>
       <c r="R44" t="n">
-        <v>6646883</v>
+        <v>6646793</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4952,12 +4946,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6406,45 +6406,49 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129976716</v>
+        <v>129976691</v>
       </c>
       <c r="B59" t="n">
-        <v>79088</v>
+        <v>98798</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>615998</v>
+        <v>616007</v>
       </c>
       <c r="R59" t="n">
-        <v>6646837</v>
+        <v>6646778</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6479,12 +6483,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>1 bukett</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6503,49 +6513,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129976691</v>
+        <v>129976716</v>
       </c>
       <c r="B60" t="n">
-        <v>98798</v>
+        <v>79088</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>616007</v>
+        <v>615998</v>
       </c>
       <c r="R60" t="n">
-        <v>6646778</v>
+        <v>6646837</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6580,18 +6586,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>1 bukett</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50796-2025 artfynd.xlsx
+++ b/artfynd/A 50796-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129806174</v>
+        <v>129806192</v>
       </c>
       <c r="B2" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616053</v>
+        <v>616113</v>
       </c>
       <c r="R2" t="n">
-        <v>6646812</v>
+        <v>6647153</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129806192</v>
+        <v>129806174</v>
       </c>
       <c r="B3" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616113</v>
+        <v>616053</v>
       </c>
       <c r="R3" t="n">
-        <v>6647153</v>
+        <v>6646812</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -872,7 +872,7 @@
         <v>129806163</v>
       </c>
       <c r="B4" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129806149</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129806166</v>
       </c>
       <c r="B7" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129806173</v>
+        <v>129806176</v>
       </c>
       <c r="B8" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616036</v>
+        <v>616099</v>
       </c>
       <c r="R8" t="n">
-        <v>6646801</v>
+        <v>6647122</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129806176</v>
+        <v>129806173</v>
       </c>
       <c r="B9" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616099</v>
+        <v>616036</v>
       </c>
       <c r="R9" t="n">
-        <v>6647122</v>
+        <v>6646801</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1464,7 +1464,7 @@
         <v>129806150</v>
       </c>
       <c r="B10" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>129806148</v>
       </c>
       <c r="B11" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129806195</v>
       </c>
       <c r="B12" t="n">
-        <v>96287</v>
+        <v>96304</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>129806172</v>
       </c>
       <c r="B13" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129806175</v>
+        <v>129806147</v>
       </c>
       <c r="B14" t="n">
-        <v>79088</v>
+        <v>91623</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615799</v>
+        <v>615859</v>
       </c>
       <c r="R14" t="n">
-        <v>6646623</v>
+        <v>6646550</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1949,7 +1949,7 @@
         <v>129806161</v>
       </c>
       <c r="B15" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129806147</v>
+        <v>129806175</v>
       </c>
       <c r="B16" t="n">
-        <v>91606</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615859</v>
+        <v>615799</v>
       </c>
       <c r="R16" t="n">
-        <v>6646550</v>
+        <v>6646623</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2145,32 +2145,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129806158</v>
+        <v>129806160</v>
       </c>
       <c r="B17" t="n">
-        <v>97669</v>
+        <v>98815</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>616104</v>
+        <v>616150</v>
       </c>
       <c r="R17" t="n">
-        <v>6646974</v>
+        <v>6646959</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2216,6 +2216,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>10. 30st</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2242,32 +2247,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129806160</v>
+        <v>129806194</v>
       </c>
       <c r="B18" t="n">
-        <v>98798</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2277,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616150</v>
+        <v>616079</v>
       </c>
       <c r="R18" t="n">
-        <v>6646959</v>
+        <v>6647068</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2313,11 +2318,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>10. 30st</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2347,7 +2347,7 @@
         <v>129806191</v>
       </c>
       <c r="B19" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2441,32 +2441,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129806194</v>
+        <v>129806158</v>
       </c>
       <c r="B20" t="n">
-        <v>79088</v>
+        <v>97686</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>616079</v>
+        <v>616104</v>
       </c>
       <c r="R20" t="n">
-        <v>6647068</v>
+        <v>6646974</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2538,32 +2538,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129806170</v>
+        <v>129806152</v>
       </c>
       <c r="B21" t="n">
-        <v>105864</v>
+        <v>57899</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>616130</v>
+        <v>615859</v>
       </c>
       <c r="R21" t="n">
-        <v>6647159</v>
+        <v>6646562</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2635,10 +2635,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129806165</v>
+        <v>129806167</v>
       </c>
       <c r="B22" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>616079</v>
+        <v>615953</v>
       </c>
       <c r="R22" t="n">
-        <v>6646998</v>
+        <v>6646752</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2737,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129806167</v>
+        <v>129806165</v>
       </c>
       <c r="B23" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615953</v>
+        <v>616079</v>
       </c>
       <c r="R23" t="n">
-        <v>6646752</v>
+        <v>6646998</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2839,32 +2839,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129806152</v>
+        <v>129806170</v>
       </c>
       <c r="B24" t="n">
-        <v>57898</v>
+        <v>105881</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615859</v>
+        <v>616130</v>
       </c>
       <c r="R24" t="n">
-        <v>6646562</v>
+        <v>6647159</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2939,7 +2939,7 @@
         <v>129806171</v>
       </c>
       <c r="B25" t="n">
-        <v>105864</v>
+        <v>105881</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>129806159</v>
       </c>
       <c r="B26" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>129806169</v>
       </c>
       <c r="B27" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>129806162</v>
       </c>
       <c r="B29" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3436,32 +3436,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129806155</v>
+        <v>129806146</v>
       </c>
       <c r="B30" t="n">
-        <v>57737</v>
+        <v>91587</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615771</v>
+        <v>615873</v>
       </c>
       <c r="R30" t="n">
-        <v>6646537</v>
+        <v>6646602</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3533,32 +3533,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129806146</v>
+        <v>129806168</v>
       </c>
       <c r="B31" t="n">
-        <v>91570</v>
+        <v>98815</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3568,10 +3568,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615873</v>
+        <v>615857</v>
       </c>
       <c r="R31" t="n">
-        <v>6646602</v>
+        <v>6646561</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3604,6 +3604,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3630,32 +3635,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129806168</v>
+        <v>129806155</v>
       </c>
       <c r="B32" t="n">
-        <v>98798</v>
+        <v>57737</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3665,10 +3670,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615857</v>
+        <v>615771</v>
       </c>
       <c r="R32" t="n">
-        <v>6646561</v>
+        <v>6646537</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3701,11 +3706,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3735,7 +3735,7 @@
         <v>129806193</v>
       </c>
       <c r="B33" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>129806151</v>
       </c>
       <c r="B34" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>129976692</v>
       </c>
       <c r="B35" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>129976700</v>
       </c>
       <c r="B36" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4140,45 +4140,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129976726</v>
+        <v>129976709</v>
       </c>
       <c r="B37" t="n">
-        <v>5177</v>
+        <v>98815</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>616026</v>
+        <v>616081</v>
       </c>
       <c r="R37" t="n">
-        <v>6646934</v>
+        <v>6647014</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4213,12 +4217,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4240,7 +4250,7 @@
         <v>129976698</v>
       </c>
       <c r="B38" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4344,49 +4354,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129976709</v>
+        <v>129976726</v>
       </c>
       <c r="B39" t="n">
-        <v>98798</v>
+        <v>5177</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>616081</v>
+        <v>616026</v>
       </c>
       <c r="R39" t="n">
-        <v>6647014</v>
+        <v>6646934</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4421,18 +4427,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4454,7 +4454,7 @@
         <v>129976690</v>
       </c>
       <c r="B40" t="n">
-        <v>97669</v>
+        <v>97686</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4548,10 +4548,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129976708</v>
+        <v>129976694</v>
       </c>
       <c r="B41" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>616088</v>
+        <v>615943</v>
       </c>
       <c r="R41" t="n">
-        <v>6647065</v>
+        <v>6646793</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>2 buketter</t>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4655,10 +4655,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129976697</v>
+        <v>129976701</v>
       </c>
       <c r="B42" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4694,10 +4694,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>616002</v>
+        <v>616166</v>
       </c>
       <c r="R42" t="n">
-        <v>6646805</v>
+        <v>6646980</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>30buketter</t>
+          <t>20 buketter</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4762,10 +4762,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129976701</v>
+        <v>129976697</v>
       </c>
       <c r="B43" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>616166</v>
+        <v>616002</v>
       </c>
       <c r="R43" t="n">
-        <v>6646980</v>
+        <v>6646805</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>20 buketter</t>
+          <t>30buketter</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4869,10 +4869,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129976694</v>
+        <v>129976708</v>
       </c>
       <c r="B44" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>615943</v>
+        <v>616088</v>
       </c>
       <c r="R44" t="n">
-        <v>6646793</v>
+        <v>6647065</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>10 buketter</t>
+          <t>2 buketter</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4979,7 +4979,7 @@
         <v>129976710</v>
       </c>
       <c r="B45" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>129976689</v>
       </c>
       <c r="B46" t="n">
-        <v>92059</v>
+        <v>92076</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>129976713</v>
       </c>
       <c r="B48" t="n">
-        <v>105864</v>
+        <v>105881</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>129976705</v>
       </c>
       <c r="B50" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>129976685</v>
       </c>
       <c r="B52" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>129976712</v>
       </c>
       <c r="B53" t="n">
-        <v>105864</v>
+        <v>105881</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>129976704</v>
       </c>
       <c r="B54" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>129976695</v>
       </c>
       <c r="B55" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6095,10 +6095,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129976699</v>
+        <v>129976706</v>
       </c>
       <c r="B56" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>615998</v>
+        <v>616129</v>
       </c>
       <c r="R56" t="n">
-        <v>6646808</v>
+        <v>6647133</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>2 buketter</t>
+          <t>30 buketter</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6202,10 +6202,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129976706</v>
+        <v>129976699</v>
       </c>
       <c r="B57" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6241,10 +6241,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>616129</v>
+        <v>615998</v>
       </c>
       <c r="R57" t="n">
-        <v>6647133</v>
+        <v>6646808</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>30 buketter</t>
+          <t>2 buketter</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6309,10 +6309,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129976717</v>
+        <v>129976716</v>
       </c>
       <c r="B58" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>616005</v>
+        <v>615998</v>
       </c>
       <c r="R58" t="n">
-        <v>6646841</v>
+        <v>6646837</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6406,49 +6406,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129976691</v>
+        <v>129976717</v>
       </c>
       <c r="B59" t="n">
-        <v>98798</v>
+        <v>79089</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>616007</v>
+        <v>616005</v>
       </c>
       <c r="R59" t="n">
-        <v>6646778</v>
+        <v>6646841</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6483,18 +6479,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>1 bukett</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6513,45 +6503,49 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129976716</v>
+        <v>129976691</v>
       </c>
       <c r="B60" t="n">
-        <v>79088</v>
+        <v>98815</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>615998</v>
+        <v>616007</v>
       </c>
       <c r="R60" t="n">
-        <v>6646837</v>
+        <v>6646778</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6586,12 +6580,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>1 bukett</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6610,32 +6610,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129976727</v>
+        <v>129976682</v>
       </c>
       <c r="B61" t="n">
-        <v>5177</v>
+        <v>91623</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6645,10 +6645,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>615998</v>
+        <v>616105</v>
       </c>
       <c r="R61" t="n">
-        <v>6646840</v>
+        <v>6647061</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6707,45 +6707,49 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129976682</v>
+        <v>129976693</v>
       </c>
       <c r="B62" t="n">
-        <v>91606</v>
+        <v>98815</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>616105</v>
+        <v>615940</v>
       </c>
       <c r="R62" t="n">
-        <v>6647061</v>
+        <v>6646762</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6780,12 +6784,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>1 bukett</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6804,49 +6814,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129976693</v>
+        <v>129976727</v>
       </c>
       <c r="B63" t="n">
-        <v>98798</v>
+        <v>5177</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>615940</v>
+        <v>615998</v>
       </c>
       <c r="R63" t="n">
-        <v>6646762</v>
+        <v>6646840</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6881,18 +6887,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>1 bukett</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6914,7 +6914,7 @@
         <v>129976684</v>
       </c>
       <c r="B64" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>129976702</v>
       </c>
       <c r="B65" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>129976711</v>
       </c>
       <c r="B66" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>129976715</v>
       </c>
       <c r="B67" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>129976707</v>
       </c>
       <c r="B69" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>129976683</v>
       </c>
       <c r="B70" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 50796-2025 artfynd.xlsx
+++ b/artfynd/A 50796-2025 artfynd.xlsx
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129806172</v>
+        <v>129806195</v>
       </c>
       <c r="B12" t="n">
-        <v>79095</v>
+        <v>96320</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615803</v>
+        <v>615759</v>
       </c>
       <c r="R12" t="n">
-        <v>6646576</v>
+        <v>6646541</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129806195</v>
+        <v>129806172</v>
       </c>
       <c r="B13" t="n">
-        <v>96320</v>
+        <v>79095</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615759</v>
+        <v>615803</v>
       </c>
       <c r="R13" t="n">
-        <v>6646541</v>
+        <v>6646576</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2145,32 +2145,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129806191</v>
+        <v>129806160</v>
       </c>
       <c r="B17" t="n">
-        <v>79095</v>
+        <v>98831</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>616225</v>
+        <v>616150</v>
       </c>
       <c r="R17" t="n">
-        <v>6647187</v>
+        <v>6646959</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2216,6 +2216,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>10. 30st</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2242,7 +2247,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129806194</v>
+        <v>129806191</v>
       </c>
       <c r="B18" t="n">
         <v>79095</v>
@@ -2277,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616079</v>
+        <v>616225</v>
       </c>
       <c r="R18" t="n">
-        <v>6647068</v>
+        <v>6647187</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2339,32 +2344,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129806160</v>
+        <v>129806194</v>
       </c>
       <c r="B19" t="n">
-        <v>98831</v>
+        <v>79095</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616150</v>
+        <v>616079</v>
       </c>
       <c r="R19" t="n">
-        <v>6646959</v>
+        <v>6647068</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2410,11 +2415,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>10. 30st</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,32 +2635,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129806165</v>
+        <v>129806170</v>
       </c>
       <c r="B22" t="n">
-        <v>98831</v>
+        <v>105897</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>616079</v>
+        <v>616130</v>
       </c>
       <c r="R22" t="n">
-        <v>6646998</v>
+        <v>6647159</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2706,11 +2706,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2737,7 +2732,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129806167</v>
+        <v>129806165</v>
       </c>
       <c r="B23" t="n">
         <v>98831</v>
@@ -2772,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615953</v>
+        <v>616079</v>
       </c>
       <c r="R23" t="n">
-        <v>6646752</v>
+        <v>6646998</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2812,7 +2807,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2839,32 +2834,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129806170</v>
+        <v>129806167</v>
       </c>
       <c r="B24" t="n">
-        <v>105897</v>
+        <v>98831</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2869,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>616130</v>
+        <v>615953</v>
       </c>
       <c r="R24" t="n">
-        <v>6647159</v>
+        <v>6646752</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2910,6 +2905,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 50796-2025 artfynd.xlsx
+++ b/artfynd/A 50796-2025 artfynd.xlsx
@@ -2145,32 +2145,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129806160</v>
+        <v>129806191</v>
       </c>
       <c r="B17" t="n">
-        <v>98831</v>
+        <v>79095</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>616150</v>
+        <v>616225</v>
       </c>
       <c r="R17" t="n">
-        <v>6646959</v>
+        <v>6647187</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2216,11 +2216,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>10. 30st</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2247,7 +2242,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129806191</v>
+        <v>129806194</v>
       </c>
       <c r="B18" t="n">
         <v>79095</v>
@@ -2282,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616225</v>
+        <v>616079</v>
       </c>
       <c r="R18" t="n">
-        <v>6647187</v>
+        <v>6647068</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2344,32 +2339,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129806194</v>
+        <v>129806160</v>
       </c>
       <c r="B19" t="n">
-        <v>79095</v>
+        <v>98831</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616079</v>
+        <v>616150</v>
       </c>
       <c r="R19" t="n">
-        <v>6647068</v>
+        <v>6646959</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2415,6 +2410,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>10. 30st</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,32 +2635,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129806170</v>
+        <v>129806165</v>
       </c>
       <c r="B22" t="n">
-        <v>105897</v>
+        <v>98831</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>616130</v>
+        <v>616079</v>
       </c>
       <c r="R22" t="n">
-        <v>6647159</v>
+        <v>6646998</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2706,6 +2706,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2732,7 +2737,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129806165</v>
+        <v>129806167</v>
       </c>
       <c r="B23" t="n">
         <v>98831</v>
@@ -2767,10 +2772,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>616079</v>
+        <v>615953</v>
       </c>
       <c r="R23" t="n">
-        <v>6646998</v>
+        <v>6646752</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2807,7 +2812,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2834,32 +2839,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129806167</v>
+        <v>129806170</v>
       </c>
       <c r="B24" t="n">
-        <v>98831</v>
+        <v>105897</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2869,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615953</v>
+        <v>616130</v>
       </c>
       <c r="R24" t="n">
-        <v>6646752</v>
+        <v>6647159</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2905,11 +2910,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4140,45 +4140,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129976726</v>
+        <v>129976698</v>
       </c>
       <c r="B37" t="n">
-        <v>5177</v>
+        <v>98831</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>616026</v>
+        <v>616004</v>
       </c>
       <c r="R37" t="n">
-        <v>6646934</v>
+        <v>6646824</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4213,12 +4217,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>6 buketter 1 blomstängel</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4237,7 +4247,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129976698</v>
+        <v>129976709</v>
       </c>
       <c r="B38" t="n">
         <v>98831</v>
@@ -4276,10 +4286,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>616004</v>
+        <v>616081</v>
       </c>
       <c r="R38" t="n">
-        <v>6646824</v>
+        <v>6647014</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4316,7 +4326,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>6 buketter 1 blomstängel</t>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4344,49 +4354,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129976709</v>
+        <v>129976726</v>
       </c>
       <c r="B39" t="n">
-        <v>98831</v>
+        <v>5177</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>616081</v>
+        <v>616026</v>
       </c>
       <c r="R39" t="n">
-        <v>6647014</v>
+        <v>6646934</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4421,18 +4427,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -6095,7 +6095,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129976699</v>
+        <v>129976706</v>
       </c>
       <c r="B56" t="n">
         <v>98831</v>
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>615998</v>
+        <v>616129</v>
       </c>
       <c r="R56" t="n">
-        <v>6646808</v>
+        <v>6647133</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>2 buketter</t>
+          <t>30 buketter</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6202,7 +6202,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129976706</v>
+        <v>129976699</v>
       </c>
       <c r="B57" t="n">
         <v>98831</v>
@@ -6241,10 +6241,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>616129</v>
+        <v>615998</v>
       </c>
       <c r="R57" t="n">
-        <v>6647133</v>
+        <v>6646808</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>30 buketter</t>
+          <t>2 buketter</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6309,45 +6309,49 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129976717</v>
+        <v>129976691</v>
       </c>
       <c r="B58" t="n">
-        <v>79095</v>
+        <v>98831</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>616005</v>
+        <v>616007</v>
       </c>
       <c r="R58" t="n">
-        <v>6646841</v>
+        <v>6646778</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6382,12 +6386,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>1 bukett</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6406,7 +6416,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129976716</v>
+        <v>129976717</v>
       </c>
       <c r="B59" t="n">
         <v>79095</v>
@@ -6441,10 +6451,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>615998</v>
+        <v>616005</v>
       </c>
       <c r="R59" t="n">
-        <v>6646837</v>
+        <v>6646841</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6503,49 +6513,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129976691</v>
+        <v>129976716</v>
       </c>
       <c r="B60" t="n">
-        <v>98831</v>
+        <v>79095</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>616007</v>
+        <v>615998</v>
       </c>
       <c r="R60" t="n">
-        <v>6646778</v>
+        <v>6646837</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6580,18 +6586,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>1 bukett</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50796-2025 artfynd.xlsx
+++ b/artfynd/A 50796-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129806192</v>
+        <v>129806163</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>98833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616113</v>
+        <v>615949</v>
       </c>
       <c r="R2" t="n">
-        <v>6647153</v>
+        <v>6646761</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129806174</v>
+        <v>129806192</v>
       </c>
       <c r="B3" t="n">
         <v>79095</v>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616053</v>
+        <v>616113</v>
       </c>
       <c r="R3" t="n">
-        <v>6646812</v>
+        <v>6647153</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129806163</v>
+        <v>129806174</v>
       </c>
       <c r="B4" t="n">
-        <v>98831</v>
+        <v>79095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615949</v>
+        <v>616053</v>
       </c>
       <c r="R4" t="n">
-        <v>6646761</v>
+        <v>6646812</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129806156</v>
+        <v>129806166</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
+        <v>98833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616164</v>
+        <v>616060</v>
       </c>
       <c r="R6" t="n">
-        <v>6647189</v>
+        <v>6646944</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1139,6 +1139,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129806166</v>
+        <v>129806156</v>
       </c>
       <c r="B7" t="n">
-        <v>98831</v>
+        <v>57738</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616060</v>
+        <v>616164</v>
       </c>
       <c r="R7" t="n">
-        <v>6646944</v>
+        <v>6647189</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1236,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1561,7 +1561,7 @@
         <v>129806148</v>
       </c>
       <c r="B11" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129806195</v>
       </c>
       <c r="B12" t="n">
-        <v>96320</v>
+        <v>96322</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129806147</v>
+        <v>129806161</v>
       </c>
       <c r="B14" t="n">
-        <v>91639</v>
+        <v>98833</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615859</v>
+        <v>616130</v>
       </c>
       <c r="R14" t="n">
-        <v>6646550</v>
+        <v>6647157</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1920,6 +1920,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>9. 15 st</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1946,32 +1951,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129806161</v>
+        <v>129806147</v>
       </c>
       <c r="B15" t="n">
-        <v>98831</v>
+        <v>91641</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>616130</v>
+        <v>615859</v>
       </c>
       <c r="R15" t="n">
-        <v>6647157</v>
+        <v>6646550</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2017,11 +2022,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>9. 15 st</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2145,7 +2145,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129806191</v>
+        <v>129806194</v>
       </c>
       <c r="B17" t="n">
         <v>79095</v>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>616225</v>
+        <v>616079</v>
       </c>
       <c r="R17" t="n">
-        <v>6647187</v>
+        <v>6647068</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2242,7 +2242,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129806194</v>
+        <v>129806191</v>
       </c>
       <c r="B18" t="n">
         <v>79095</v>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616079</v>
+        <v>616225</v>
       </c>
       <c r="R18" t="n">
-        <v>6647068</v>
+        <v>6647187</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2339,32 +2339,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129806160</v>
+        <v>129806158</v>
       </c>
       <c r="B19" t="n">
-        <v>98831</v>
+        <v>97704</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616150</v>
+        <v>616104</v>
       </c>
       <c r="R19" t="n">
-        <v>6646959</v>
+        <v>6646974</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2410,11 +2410,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>10. 30st</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2441,32 +2436,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129806158</v>
+        <v>129806160</v>
       </c>
       <c r="B20" t="n">
-        <v>97702</v>
+        <v>98833</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>616104</v>
+        <v>616150</v>
       </c>
       <c r="R20" t="n">
-        <v>6646974</v>
+        <v>6646959</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2512,6 +2507,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>10. 30st</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2538,32 +2538,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129806152</v>
+        <v>129806170</v>
       </c>
       <c r="B21" t="n">
-        <v>57900</v>
+        <v>105900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615859</v>
+        <v>616130</v>
       </c>
       <c r="R21" t="n">
-        <v>6646562</v>
+        <v>6647159</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2635,32 +2635,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129806165</v>
+        <v>129806152</v>
       </c>
       <c r="B22" t="n">
-        <v>98831</v>
+        <v>57900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>616079</v>
+        <v>615859</v>
       </c>
       <c r="R22" t="n">
-        <v>6646998</v>
+        <v>6646562</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2706,11 +2706,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2737,10 +2732,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129806167</v>
+        <v>129806165</v>
       </c>
       <c r="B23" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2772,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615953</v>
+        <v>616079</v>
       </c>
       <c r="R23" t="n">
-        <v>6646752</v>
+        <v>6646998</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2812,7 +2807,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2839,32 +2834,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129806170</v>
+        <v>129806167</v>
       </c>
       <c r="B24" t="n">
-        <v>105897</v>
+        <v>98833</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2869,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>616130</v>
+        <v>615953</v>
       </c>
       <c r="R24" t="n">
-        <v>6647159</v>
+        <v>6646752</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2910,6 +2905,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2939,7 +2939,7 @@
         <v>129806171</v>
       </c>
       <c r="B25" t="n">
-        <v>105897</v>
+        <v>105900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129806169</v>
+        <v>129806159</v>
       </c>
       <c r="B26" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>615861</v>
+        <v>615789</v>
       </c>
       <c r="R26" t="n">
-        <v>6646557</v>
+        <v>6646577</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3. 8 st</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3135,10 +3135,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129806159</v>
+        <v>129806169</v>
       </c>
       <c r="B27" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>615789</v>
+        <v>615861</v>
       </c>
       <c r="R27" t="n">
-        <v>6646577</v>
+        <v>6646557</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>3. 8 st</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3337,7 +3337,7 @@
         <v>129806162</v>
       </c>
       <c r="B29" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3436,32 +3436,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129806146</v>
+        <v>129806168</v>
       </c>
       <c r="B30" t="n">
-        <v>91603</v>
+        <v>98833</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615873</v>
+        <v>615857</v>
       </c>
       <c r="R30" t="n">
-        <v>6646602</v>
+        <v>6646561</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3507,6 +3507,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3630,32 +3635,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129806168</v>
+        <v>129806146</v>
       </c>
       <c r="B32" t="n">
-        <v>98831</v>
+        <v>91605</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3665,10 +3670,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615857</v>
+        <v>615873</v>
       </c>
       <c r="R32" t="n">
-        <v>6646561</v>
+        <v>6646602</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3701,11 +3706,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3929,7 +3929,7 @@
         <v>129976692</v>
       </c>
       <c r="B35" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>129976700</v>
       </c>
       <c r="B36" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4140,49 +4140,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129976698</v>
+        <v>129976726</v>
       </c>
       <c r="B37" t="n">
-        <v>98831</v>
+        <v>5177</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>616004</v>
+        <v>616026</v>
       </c>
       <c r="R37" t="n">
-        <v>6646824</v>
+        <v>6646934</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4217,18 +4213,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>6 buketter 1 blomstängel</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4247,10 +4237,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129976709</v>
+        <v>129976698</v>
       </c>
       <c r="B38" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4286,10 +4276,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>616081</v>
+        <v>616004</v>
       </c>
       <c r="R38" t="n">
-        <v>6647014</v>
+        <v>6646824</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4326,7 +4316,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>10 buketter</t>
+          <t>6 buketter 1 blomstängel</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4354,45 +4344,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129976726</v>
+        <v>129976709</v>
       </c>
       <c r="B39" t="n">
-        <v>5177</v>
+        <v>98833</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>616026</v>
+        <v>616081</v>
       </c>
       <c r="R39" t="n">
-        <v>6646934</v>
+        <v>6647014</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4427,12 +4421,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4454,7 +4454,7 @@
         <v>129976708</v>
       </c>
       <c r="B40" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>129976697</v>
       </c>
       <c r="B41" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>129976701</v>
       </c>
       <c r="B42" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>129976694</v>
       </c>
       <c r="B43" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>129976690</v>
       </c>
       <c r="B44" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>129976710</v>
       </c>
       <c r="B45" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5083,32 +5083,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129976686</v>
+        <v>129976689</v>
       </c>
       <c r="B46" t="n">
-        <v>57738</v>
+        <v>92094</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>616291</v>
+        <v>615951</v>
       </c>
       <c r="R46" t="n">
-        <v>6647141</v>
+        <v>6646840</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5180,32 +5180,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129976689</v>
+        <v>129976686</v>
       </c>
       <c r="B47" t="n">
-        <v>92092</v>
+        <v>57738</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5215,10 +5215,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>615951</v>
+        <v>616291</v>
       </c>
       <c r="R47" t="n">
-        <v>6646840</v>
+        <v>6647141</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5280,7 +5280,7 @@
         <v>129976713</v>
       </c>
       <c r="B48" t="n">
-        <v>105897</v>
+        <v>105900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>129976705</v>
       </c>
       <c r="B50" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5681,32 +5681,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129976712</v>
+        <v>129976685</v>
       </c>
       <c r="B52" t="n">
-        <v>105897</v>
+        <v>57900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5716,10 +5716,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>616148</v>
+        <v>616099</v>
       </c>
       <c r="R52" t="n">
-        <v>6646963</v>
+        <v>6647081</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5754,18 +5754,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>8 buketter</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5784,32 +5778,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129976685</v>
+        <v>129976712</v>
       </c>
       <c r="B53" t="n">
-        <v>57900</v>
+        <v>105900</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5819,10 +5813,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>616099</v>
+        <v>616148</v>
       </c>
       <c r="R53" t="n">
-        <v>6647081</v>
+        <v>6646963</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5857,12 +5851,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>8 buketter</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5884,7 +5884,7 @@
         <v>129976704</v>
       </c>
       <c r="B54" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>129976695</v>
       </c>
       <c r="B55" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6095,10 +6095,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129976706</v>
+        <v>129976699</v>
       </c>
       <c r="B56" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>616129</v>
+        <v>615998</v>
       </c>
       <c r="R56" t="n">
-        <v>6647133</v>
+        <v>6646808</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>30 buketter</t>
+          <t>2 buketter</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6202,10 +6202,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129976699</v>
+        <v>129976706</v>
       </c>
       <c r="B57" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6241,10 +6241,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>615998</v>
+        <v>616129</v>
       </c>
       <c r="R57" t="n">
-        <v>6646808</v>
+        <v>6647133</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>2 buketter</t>
+          <t>30 buketter</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6312,7 +6312,7 @@
         <v>129976691</v>
       </c>
       <c r="B58" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>129976682</v>
       </c>
       <c r="B61" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6707,45 +6707,49 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129976727</v>
+        <v>129976693</v>
       </c>
       <c r="B62" t="n">
-        <v>5177</v>
+        <v>98833</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>615998</v>
+        <v>615940</v>
       </c>
       <c r="R62" t="n">
-        <v>6646840</v>
+        <v>6646762</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6780,12 +6784,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>1 bukett</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6804,49 +6814,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129976693</v>
+        <v>129976727</v>
       </c>
       <c r="B63" t="n">
-        <v>98831</v>
+        <v>5177</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>615940</v>
+        <v>615998</v>
       </c>
       <c r="R63" t="n">
-        <v>6646762</v>
+        <v>6646840</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6881,18 +6887,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>1 bukett</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6914,7 +6914,7 @@
         <v>129976684</v>
       </c>
       <c r="B64" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>129976702</v>
       </c>
       <c r="B65" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>129976711</v>
       </c>
       <c r="B66" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>129976707</v>
       </c>
       <c r="B69" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>129976683</v>
       </c>
       <c r="B70" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 50796-2025 artfynd.xlsx
+++ b/artfynd/A 50796-2025 artfynd.xlsx
@@ -3929,7 +3929,7 @@
         <v>129976692</v>
       </c>
       <c r="B35" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>129976700</v>
       </c>
       <c r="B36" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4140,45 +4140,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129976726</v>
+        <v>129976709</v>
       </c>
       <c r="B37" t="n">
-        <v>5177</v>
+        <v>98920</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>616026</v>
+        <v>616081</v>
       </c>
       <c r="R37" t="n">
-        <v>6646934</v>
+        <v>6647014</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4213,12 +4217,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4237,49 +4247,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129976698</v>
+        <v>129976726</v>
       </c>
       <c r="B38" t="n">
-        <v>98833</v>
+        <v>5177</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>616004</v>
+        <v>616026</v>
       </c>
       <c r="R38" t="n">
-        <v>6646824</v>
+        <v>6646934</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4314,18 +4320,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>6 buketter 1 blomstängel</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4344,10 +4344,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129976709</v>
+        <v>129976698</v>
       </c>
       <c r="B39" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4383,10 +4383,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>616081</v>
+        <v>616004</v>
       </c>
       <c r="R39" t="n">
-        <v>6647014</v>
+        <v>6646824</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>10 buketter</t>
+          <t>6 buketter 1 blomstängel</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4451,10 +4451,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129976708</v>
+        <v>129976697</v>
       </c>
       <c r="B40" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4490,10 +4490,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>616088</v>
+        <v>616002</v>
       </c>
       <c r="R40" t="n">
-        <v>6647065</v>
+        <v>6646805</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>2 buketter</t>
+          <t>30buketter</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4558,49 +4558,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129976697</v>
+        <v>129976690</v>
       </c>
       <c r="B41" t="n">
-        <v>98833</v>
+        <v>97791</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>616002</v>
+        <v>616096</v>
       </c>
       <c r="R41" t="n">
-        <v>6646805</v>
+        <v>6646883</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4635,18 +4631,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>30buketter</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4668,7 +4658,7 @@
         <v>129976701</v>
       </c>
       <c r="B42" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4772,10 +4762,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129976694</v>
+        <v>129976708</v>
       </c>
       <c r="B43" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4811,10 +4801,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>615943</v>
+        <v>616088</v>
       </c>
       <c r="R43" t="n">
-        <v>6646793</v>
+        <v>6647065</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4851,7 +4841,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>10 buketter</t>
+          <t>2 buketter</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4879,45 +4869,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129976690</v>
+        <v>129976694</v>
       </c>
       <c r="B44" t="n">
-        <v>97704</v>
+        <v>98920</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>616096</v>
+        <v>615943</v>
       </c>
       <c r="R44" t="n">
-        <v>6646883</v>
+        <v>6646793</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4952,12 +4946,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4979,7 +4979,7 @@
         <v>129976710</v>
       </c>
       <c r="B45" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5083,32 +5083,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129976689</v>
+        <v>129976713</v>
       </c>
       <c r="B46" t="n">
-        <v>92094</v>
+        <v>105987</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>615951</v>
+        <v>616084</v>
       </c>
       <c r="R46" t="n">
-        <v>6646840</v>
+        <v>6647010</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5156,12 +5156,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>8 buketter</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5180,32 +5186,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129976686</v>
+        <v>129976689</v>
       </c>
       <c r="B47" t="n">
-        <v>57738</v>
+        <v>92181</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5215,10 +5221,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>616291</v>
+        <v>615951</v>
       </c>
       <c r="R47" t="n">
-        <v>6647141</v>
+        <v>6646840</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5277,32 +5283,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129976713</v>
+        <v>129976686</v>
       </c>
       <c r="B48" t="n">
-        <v>105900</v>
+        <v>57823</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5312,10 +5318,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>616084</v>
+        <v>616291</v>
       </c>
       <c r="R48" t="n">
-        <v>6647010</v>
+        <v>6647141</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5350,18 +5356,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>8 buketter</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5480,7 +5480,7 @@
         <v>129976705</v>
       </c>
       <c r="B50" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>129976687</v>
       </c>
       <c r="B51" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>129976685</v>
       </c>
       <c r="B52" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>129976712</v>
       </c>
       <c r="B53" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>129976704</v>
       </c>
       <c r="B54" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>129976695</v>
       </c>
       <c r="B55" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6095,10 +6095,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129976699</v>
+        <v>129976706</v>
       </c>
       <c r="B56" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>615998</v>
+        <v>616129</v>
       </c>
       <c r="R56" t="n">
-        <v>6646808</v>
+        <v>6647133</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>2 buketter</t>
+          <t>30 buketter</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6202,10 +6202,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129976706</v>
+        <v>129976699</v>
       </c>
       <c r="B57" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6241,10 +6241,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>616129</v>
+        <v>615998</v>
       </c>
       <c r="R57" t="n">
-        <v>6647133</v>
+        <v>6646808</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>30 buketter</t>
+          <t>2 buketter</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6309,49 +6309,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129976691</v>
+        <v>129976717</v>
       </c>
       <c r="B58" t="n">
-        <v>98833</v>
+        <v>79180</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>616007</v>
+        <v>616005</v>
       </c>
       <c r="R58" t="n">
-        <v>6646778</v>
+        <v>6646841</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6386,18 +6382,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>1 bukett</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6416,10 +6406,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129976717</v>
+        <v>129976716</v>
       </c>
       <c r="B59" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6451,10 +6441,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>616005</v>
+        <v>615998</v>
       </c>
       <c r="R59" t="n">
-        <v>6646841</v>
+        <v>6646837</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6513,45 +6503,49 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129976716</v>
+        <v>129976691</v>
       </c>
       <c r="B60" t="n">
-        <v>79095</v>
+        <v>98920</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>615998</v>
+        <v>616007</v>
       </c>
       <c r="R60" t="n">
-        <v>6646837</v>
+        <v>6646778</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6586,12 +6580,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>1 bukett</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6613,7 +6613,7 @@
         <v>129976682</v>
       </c>
       <c r="B61" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>129976693</v>
       </c>
       <c r="B62" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>129976684</v>
       </c>
       <c r="B64" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>129976702</v>
       </c>
       <c r="B65" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>129976711</v>
       </c>
       <c r="B66" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7222,45 +7222,49 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129976715</v>
+        <v>129976707</v>
       </c>
       <c r="B67" t="n">
-        <v>79095</v>
+        <v>98920</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>616081</v>
+        <v>616125</v>
       </c>
       <c r="R67" t="n">
-        <v>6647102</v>
+        <v>6647116</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7297,7 +7301,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Rikligt på flera träd</t>
+          <t>2 buketter</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7325,10 +7329,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129976688</v>
+        <v>129976715</v>
       </c>
       <c r="B68" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7336,21 +7340,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7360,10 +7364,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>615955</v>
+        <v>616081</v>
       </c>
       <c r="R68" t="n">
-        <v>6646826</v>
+        <v>6647102</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7398,12 +7402,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt på flera träd</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7422,49 +7432,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129976707</v>
+        <v>129976688</v>
       </c>
       <c r="B69" t="n">
-        <v>98833</v>
+        <v>57823</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>616125</v>
+        <v>615955</v>
       </c>
       <c r="R69" t="n">
-        <v>6647116</v>
+        <v>6646826</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7499,18 +7505,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>2 buketter</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7532,7 +7532,7 @@
         <v>129976683</v>
       </c>
       <c r="B70" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 50796-2025 artfynd.xlsx
+++ b/artfynd/A 50796-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129806163</v>
+        <v>129806147</v>
       </c>
       <c r="B2" t="n">
-        <v>98833</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615949</v>
+        <v>615859</v>
       </c>
       <c r="R2" t="n">
-        <v>6646761</v>
+        <v>6646550</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129806192</v>
+        <v>129806148</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616113</v>
+        <v>615864</v>
       </c>
       <c r="R3" t="n">
-        <v>6647153</v>
+        <v>6646555</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129806174</v>
+        <v>129976682</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616053</v>
+        <v>616105</v>
       </c>
       <c r="R4" t="n">
-        <v>6646812</v>
+        <v>6647061</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -939,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129806149</v>
+        <v>129976683</v>
       </c>
       <c r="B5" t="n">
-        <v>57900</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616122</v>
+        <v>615962</v>
       </c>
       <c r="R5" t="n">
-        <v>6647126</v>
+        <v>6646716</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1036,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129806166</v>
+        <v>129976684</v>
       </c>
       <c r="B6" t="n">
-        <v>98833</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616060</v>
+        <v>615950</v>
       </c>
       <c r="R6" t="n">
-        <v>6646944</v>
+        <v>6646831</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1133,17 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129806156</v>
+        <v>129976689</v>
       </c>
       <c r="B7" t="n">
-        <v>57738</v>
+        <v>92369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616164</v>
+        <v>615951</v>
       </c>
       <c r="R7" t="n">
-        <v>6647189</v>
+        <v>6646840</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1235,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129806176</v>
+        <v>129806195</v>
       </c>
       <c r="B8" t="n">
-        <v>79095</v>
+        <v>96601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616099</v>
+        <v>615759</v>
       </c>
       <c r="R8" t="n">
-        <v>6647122</v>
+        <v>6646541</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1364,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129806173</v>
+        <v>129806146</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616036</v>
+        <v>615873</v>
       </c>
       <c r="R9" t="n">
-        <v>6646801</v>
+        <v>6646602</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129806150</v>
+        <v>129806172</v>
       </c>
       <c r="B10" t="n">
-        <v>57900</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616253</v>
+        <v>615803</v>
       </c>
       <c r="R10" t="n">
-        <v>6647113</v>
+        <v>6646576</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1558,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129806148</v>
+        <v>129806173</v>
       </c>
       <c r="B11" t="n">
-        <v>91641</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615864</v>
+        <v>616036</v>
       </c>
       <c r="R11" t="n">
-        <v>6646555</v>
+        <v>6646801</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1655,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129806195</v>
+        <v>129806174</v>
       </c>
       <c r="B12" t="n">
-        <v>96322</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615759</v>
+        <v>616053</v>
       </c>
       <c r="R12" t="n">
-        <v>6646541</v>
+        <v>6646812</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1752,14 +1742,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129806172</v>
+        <v>129806175</v>
       </c>
       <c r="B13" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1787,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615803</v>
+        <v>615799</v>
       </c>
       <c r="R13" t="n">
-        <v>6646576</v>
+        <v>6646623</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1849,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129806161</v>
+        <v>129806176</v>
       </c>
       <c r="B14" t="n">
-        <v>98833</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>616130</v>
+        <v>616099</v>
       </c>
       <c r="R14" t="n">
-        <v>6647157</v>
+        <v>6647122</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1920,11 +1910,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>9. 15 st</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1951,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129806147</v>
+        <v>129806177</v>
       </c>
       <c r="B15" t="n">
-        <v>91641</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615859</v>
+        <v>616079</v>
       </c>
       <c r="R15" t="n">
-        <v>6646550</v>
+        <v>6647113</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2048,14 +2033,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129806175</v>
+        <v>129806191</v>
       </c>
       <c r="B16" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2083,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615799</v>
+        <v>616225</v>
       </c>
       <c r="R16" t="n">
-        <v>6646623</v>
+        <v>6647187</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2145,14 +2130,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129806194</v>
+        <v>129806192</v>
       </c>
       <c r="B17" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2180,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>616079</v>
+        <v>616113</v>
       </c>
       <c r="R17" t="n">
-        <v>6647068</v>
+        <v>6647153</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2242,14 +2227,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129806191</v>
+        <v>129806193</v>
       </c>
       <c r="B18" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2277,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616225</v>
+        <v>616094</v>
       </c>
       <c r="R18" t="n">
-        <v>6647187</v>
+        <v>6647111</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2339,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129806158</v>
+        <v>129806194</v>
       </c>
       <c r="B19" t="n">
-        <v>97704</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616104</v>
+        <v>616079</v>
       </c>
       <c r="R19" t="n">
-        <v>6646974</v>
+        <v>6647068</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2436,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129806160</v>
+        <v>129976715</v>
       </c>
       <c r="B20" t="n">
-        <v>98833</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2471,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>616150</v>
+        <v>616081</v>
       </c>
       <c r="R20" t="n">
-        <v>6646959</v>
+        <v>6647102</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2501,17 +2486,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>10. 30st</t>
+          <t>Rikligt på flera träd</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2520,6 +2505,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2538,32 +2524,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129806170</v>
+        <v>129976716</v>
       </c>
       <c r="B21" t="n">
-        <v>105900</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2559,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>616130</v>
+        <v>615998</v>
       </c>
       <c r="R21" t="n">
-        <v>6647159</v>
+        <v>6646837</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2603,12 +2589,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2635,32 +2621,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129806152</v>
+        <v>129976717</v>
       </c>
       <c r="B22" t="n">
-        <v>57900</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>615859</v>
+        <v>616005</v>
       </c>
       <c r="R22" t="n">
-        <v>6646562</v>
+        <v>6646841</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2700,12 +2686,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2732,32 +2718,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129806165</v>
+        <v>129806155</v>
       </c>
       <c r="B23" t="n">
-        <v>98833</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2767,10 +2753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>616079</v>
+        <v>615771</v>
       </c>
       <c r="R23" t="n">
-        <v>6646998</v>
+        <v>6646537</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2803,11 +2789,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2834,32 +2815,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129806167</v>
+        <v>129806156</v>
       </c>
       <c r="B24" t="n">
-        <v>98833</v>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2869,10 +2850,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615953</v>
+        <v>616164</v>
       </c>
       <c r="R24" t="n">
-        <v>6646752</v>
+        <v>6647189</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2905,11 +2886,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2936,10 +2912,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129806171</v>
+        <v>129806157</v>
       </c>
       <c r="B25" t="n">
-        <v>105900</v>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,21 +2923,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2947,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>615993</v>
+        <v>616121</v>
       </c>
       <c r="R25" t="n">
-        <v>6646768</v>
+        <v>6646931</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3033,32 +3009,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129806159</v>
+        <v>129976686</v>
       </c>
       <c r="B26" t="n">
-        <v>98833</v>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3044,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>615789</v>
+        <v>616291</v>
       </c>
       <c r="R26" t="n">
-        <v>6646577</v>
+        <v>6647141</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3098,17 +3074,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>3. 8 st</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3135,32 +3106,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129806169</v>
+        <v>129976687</v>
       </c>
       <c r="B27" t="n">
-        <v>98833</v>
+        <v>57950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3170,10 +3141,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>615861</v>
+        <v>616091</v>
       </c>
       <c r="R27" t="n">
-        <v>6646557</v>
+        <v>6647065</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3200,17 +3171,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3237,14 +3203,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129806157</v>
+        <v>129976688</v>
       </c>
       <c r="B28" t="n">
-        <v>57738</v>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3272,10 +3238,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>616121</v>
+        <v>615955</v>
       </c>
       <c r="R28" t="n">
-        <v>6646931</v>
+        <v>6646826</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3302,12 +3268,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3334,32 +3300,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129806162</v>
+        <v>129976726</v>
       </c>
       <c r="B29" t="n">
-        <v>98833</v>
+        <v>5179</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3369,10 +3335,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>616053</v>
+        <v>616026</v>
       </c>
       <c r="R29" t="n">
-        <v>6646949</v>
+        <v>6646934</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3399,17 +3365,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>6. 10 st</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3436,32 +3397,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129806168</v>
+        <v>129976727</v>
       </c>
       <c r="B30" t="n">
-        <v>98833</v>
+        <v>5179</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3471,10 +3432,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615857</v>
+        <v>615998</v>
       </c>
       <c r="R30" t="n">
-        <v>6646561</v>
+        <v>6646840</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3501,17 +3462,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3538,10 +3494,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129806155</v>
+        <v>129806149</v>
       </c>
       <c r="B31" t="n">
-        <v>57738</v>
+        <v>58114</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3549,21 +3505,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3573,10 +3529,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615771</v>
+        <v>616122</v>
       </c>
       <c r="R31" t="n">
-        <v>6646537</v>
+        <v>6647126</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3635,32 +3591,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129806146</v>
+        <v>129806150</v>
       </c>
       <c r="B32" t="n">
-        <v>91605</v>
+        <v>58114</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3670,10 +3626,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615873</v>
+        <v>616253</v>
       </c>
       <c r="R32" t="n">
-        <v>6646602</v>
+        <v>6647113</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3732,10 +3688,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129806193</v>
+        <v>129806151</v>
       </c>
       <c r="B33" t="n">
-        <v>79095</v>
+        <v>58114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3743,21 +3699,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3767,10 +3723,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>616094</v>
+        <v>615807</v>
       </c>
       <c r="R33" t="n">
-        <v>6647111</v>
+        <v>6646606</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3829,10 +3785,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129806151</v>
+        <v>129806152</v>
       </c>
       <c r="B34" t="n">
-        <v>57900</v>
+        <v>58114</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3864,10 +3820,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>615807</v>
+        <v>615859</v>
       </c>
       <c r="R34" t="n">
-        <v>6646606</v>
+        <v>6646562</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3926,49 +3882,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129976692</v>
+        <v>129976685</v>
       </c>
       <c r="B35" t="n">
-        <v>98920</v>
+        <v>58114</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>615954</v>
+        <v>616099</v>
       </c>
       <c r="R35" t="n">
-        <v>6646724</v>
+        <v>6647081</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4003,18 +3955,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>8 buketter</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4033,49 +3979,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129976700</v>
+        <v>129976681</v>
       </c>
       <c r="B36" t="n">
-        <v>98920</v>
+        <v>5199</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>616077</v>
+        <v>615950</v>
       </c>
       <c r="R36" t="n">
-        <v>6646922</v>
+        <v>6646824</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4110,18 +4052,12 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>25 buketter</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4140,32 +4076,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129976726</v>
+        <v>129806159</v>
       </c>
       <c r="B37" t="n">
-        <v>5177</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4175,10 +4111,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>616026</v>
+        <v>615789</v>
       </c>
       <c r="R37" t="n">
-        <v>6646934</v>
+        <v>6646577</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4205,12 +4141,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>3. 8 st</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4237,10 +4178,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129976698</v>
+        <v>129806160</v>
       </c>
       <c r="B38" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4266,20 +4207,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>616004</v>
+        <v>616150</v>
       </c>
       <c r="R38" t="n">
-        <v>6646824</v>
+        <v>6646959</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4306,17 +4243,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>6 buketter 1 blomstängel</t>
+          <t>10. 30st</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4325,7 +4262,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4344,10 +4280,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129976709</v>
+        <v>129806161</v>
       </c>
       <c r="B39" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4373,20 +4309,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>616081</v>
+        <v>616130</v>
       </c>
       <c r="R39" t="n">
-        <v>6647014</v>
+        <v>6647157</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4413,17 +4345,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>10 buketter</t>
+          <t>9. 15 st</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4432,7 +4364,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4451,10 +4382,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129976708</v>
+        <v>129806162</v>
       </c>
       <c r="B40" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4480,20 +4411,16 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>616088</v>
+        <v>616053</v>
       </c>
       <c r="R40" t="n">
-        <v>6647065</v>
+        <v>6646949</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4520,17 +4447,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>2 buketter</t>
+          <t>6. 10 st</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4539,7 +4466,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4558,10 +4484,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129976697</v>
+        <v>129806163</v>
       </c>
       <c r="B41" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4587,20 +4513,16 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>616002</v>
+        <v>615949</v>
       </c>
       <c r="R41" t="n">
-        <v>6646805</v>
+        <v>6646761</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4627,17 +4549,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>30buketter</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4646,7 +4568,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4665,10 +4586,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129976701</v>
+        <v>129806165</v>
       </c>
       <c r="B42" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4694,20 +4615,16 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>616166</v>
+        <v>616079</v>
       </c>
       <c r="R42" t="n">
-        <v>6646980</v>
+        <v>6646998</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4734,17 +4651,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>20 buketter</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4753,7 +4670,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4772,10 +4688,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129976694</v>
+        <v>129806166</v>
       </c>
       <c r="B43" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4801,20 +4717,16 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>615943</v>
+        <v>616060</v>
       </c>
       <c r="R43" t="n">
-        <v>6646793</v>
+        <v>6646944</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4841,17 +4753,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>10 buketter</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4860,7 +4772,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4879,32 +4790,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129976690</v>
+        <v>129806167</v>
       </c>
       <c r="B44" t="n">
-        <v>97791</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4914,10 +4825,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>616096</v>
+        <v>615953</v>
       </c>
       <c r="R44" t="n">
-        <v>6646883</v>
+        <v>6646752</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4944,12 +4855,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4976,10 +4892,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129976710</v>
+        <v>129806168</v>
       </c>
       <c r="B45" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5005,20 +4921,16 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>616105</v>
+        <v>615857</v>
       </c>
       <c r="R45" t="n">
-        <v>6646876</v>
+        <v>6646561</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5045,17 +4957,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>4 buketter</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5064,7 +4976,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5083,10 +4994,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129976689</v>
+        <v>129806169</v>
       </c>
       <c r="B46" t="n">
-        <v>92181</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5094,21 +5005,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5118,10 +5029,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>615951</v>
+        <v>615861</v>
       </c>
       <c r="R46" t="n">
-        <v>6646840</v>
+        <v>6646557</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5148,12 +5059,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5180,45 +5096,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129976686</v>
+        <v>129976691</v>
       </c>
       <c r="B47" t="n">
-        <v>57823</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>616291</v>
+        <v>616007</v>
       </c>
       <c r="R47" t="n">
-        <v>6647141</v>
+        <v>6646778</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5253,12 +5173,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>1 bukett</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5277,45 +5203,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129976713</v>
+        <v>129976692</v>
       </c>
       <c r="B48" t="n">
-        <v>105987</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>616084</v>
+        <v>615954</v>
       </c>
       <c r="R48" t="n">
-        <v>6647010</v>
+        <v>6646724</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5380,45 +5310,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129976681</v>
+        <v>129976693</v>
       </c>
       <c r="B49" t="n">
-        <v>5197</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>615950</v>
+        <v>615940</v>
       </c>
       <c r="R49" t="n">
-        <v>6646824</v>
+        <v>6646762</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5453,12 +5387,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>1 bukett</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5477,10 +5417,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129976705</v>
+        <v>129976694</v>
       </c>
       <c r="B50" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5516,10 +5456,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>616139</v>
+        <v>615943</v>
       </c>
       <c r="R50" t="n">
-        <v>6646955</v>
+        <v>6646793</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5556,7 +5496,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>15 buketter</t>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5584,45 +5524,49 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129976687</v>
+        <v>129976695</v>
       </c>
       <c r="B51" t="n">
-        <v>57823</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>616091</v>
+        <v>616007</v>
       </c>
       <c r="R51" t="n">
-        <v>6647065</v>
+        <v>6646800</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5657,12 +5601,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>3 buketter</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5681,45 +5631,49 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129976685</v>
+        <v>129976697</v>
       </c>
       <c r="B52" t="n">
-        <v>57985</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>616099</v>
+        <v>616002</v>
       </c>
       <c r="R52" t="n">
-        <v>6647081</v>
+        <v>6646805</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5754,12 +5708,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>30buketter</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5778,45 +5738,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129976712</v>
+        <v>129976698</v>
       </c>
       <c r="B53" t="n">
-        <v>105987</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>616148</v>
+        <v>616004</v>
       </c>
       <c r="R53" t="n">
-        <v>6646963</v>
+        <v>6646824</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5853,7 +5817,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>8 buketter</t>
+          <t>6 buketter 1 blomstängel</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5881,10 +5845,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129976704</v>
+        <v>129976699</v>
       </c>
       <c r="B54" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5920,10 +5884,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>616200</v>
+        <v>615998</v>
       </c>
       <c r="R54" t="n">
-        <v>6647015</v>
+        <v>6646808</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5960,7 +5924,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>6 buketter</t>
+          <t>2 buketter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5988,10 +5952,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129976695</v>
+        <v>129976700</v>
       </c>
       <c r="B55" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6027,10 +5991,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>616007</v>
+        <v>616077</v>
       </c>
       <c r="R55" t="n">
-        <v>6646800</v>
+        <v>6646922</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6067,7 +6031,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>3 buketter</t>
+          <t>25 buketter</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6095,10 +6059,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129976699</v>
+        <v>129976701</v>
       </c>
       <c r="B56" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6134,10 +6098,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>615998</v>
+        <v>616166</v>
       </c>
       <c r="R56" t="n">
-        <v>6646808</v>
+        <v>6646980</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6174,7 +6138,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>2 buketter</t>
+          <t>20 buketter</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6202,10 +6166,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129976706</v>
+        <v>129976702</v>
       </c>
       <c r="B57" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6241,10 +6205,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>616129</v>
+        <v>616192</v>
       </c>
       <c r="R57" t="n">
-        <v>6647133</v>
+        <v>6647016</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6281,7 +6245,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>30 buketter</t>
+          <t>4 buketter</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6309,10 +6273,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129976691</v>
+        <v>129976704</v>
       </c>
       <c r="B58" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6348,10 +6312,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>616007</v>
+        <v>616200</v>
       </c>
       <c r="R58" t="n">
-        <v>6646778</v>
+        <v>6647015</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6388,7 +6352,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>1 bukett</t>
+          <t>6 buketter</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6416,45 +6380,49 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129976716</v>
+        <v>129976705</v>
       </c>
       <c r="B59" t="n">
-        <v>79180</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>615998</v>
+        <v>616139</v>
       </c>
       <c r="R59" t="n">
-        <v>6646837</v>
+        <v>6646955</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6489,12 +6457,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>15 buketter</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6513,45 +6487,49 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129976717</v>
+        <v>129976706</v>
       </c>
       <c r="B60" t="n">
-        <v>79180</v>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>616005</v>
+        <v>616129</v>
       </c>
       <c r="R60" t="n">
-        <v>6646841</v>
+        <v>6647133</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6586,12 +6564,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>30 buketter</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6610,45 +6594,49 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129976682</v>
+        <v>129976707</v>
       </c>
       <c r="B61" t="n">
-        <v>91728</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>616105</v>
+        <v>616125</v>
       </c>
       <c r="R61" t="n">
-        <v>6647061</v>
+        <v>6647116</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6683,12 +6671,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>2 buketter</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6707,10 +6701,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129976693</v>
+        <v>129976708</v>
       </c>
       <c r="B62" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6746,10 +6740,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>615940</v>
+        <v>616088</v>
       </c>
       <c r="R62" t="n">
-        <v>6646762</v>
+        <v>6647065</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6786,7 +6780,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>1 bukett</t>
+          <t>2 buketter</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6814,45 +6808,49 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129976727</v>
+        <v>129976709</v>
       </c>
       <c r="B63" t="n">
-        <v>5177</v>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>615998</v>
+        <v>616081</v>
       </c>
       <c r="R63" t="n">
-        <v>6646840</v>
+        <v>6647014</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6887,12 +6885,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6911,45 +6915,49 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129976684</v>
+        <v>129976710</v>
       </c>
       <c r="B64" t="n">
-        <v>91728</v>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>615950</v>
+        <v>616105</v>
       </c>
       <c r="R64" t="n">
-        <v>6646831</v>
+        <v>6646876</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6984,12 +6992,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>4 buketter</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7008,10 +7022,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129976702</v>
+        <v>129976711</v>
       </c>
       <c r="B65" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7047,10 +7061,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>616192</v>
+        <v>616085</v>
       </c>
       <c r="R65" t="n">
-        <v>6647016</v>
+        <v>6647012</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7087,7 +7101,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>4 buketter</t>
+          <t>20 buketter</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7115,49 +7129,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129976711</v>
+        <v>129806170</v>
       </c>
       <c r="B66" t="n">
-        <v>98920</v>
+        <v>106243</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>616085</v>
+        <v>616130</v>
       </c>
       <c r="R66" t="n">
-        <v>6647012</v>
+        <v>6647159</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7184,17 +7194,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>20 buketter</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7203,7 +7208,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7222,32 +7226,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129976715</v>
+        <v>129806171</v>
       </c>
       <c r="B67" t="n">
-        <v>79180</v>
+        <v>106243</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7257,10 +7261,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>616081</v>
+        <v>615993</v>
       </c>
       <c r="R67" t="n">
-        <v>6647102</v>
+        <v>6646768</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7287,17 +7291,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt på flera träd</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7306,7 +7305,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7325,32 +7323,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129976688</v>
+        <v>129976712</v>
       </c>
       <c r="B68" t="n">
-        <v>57823</v>
+        <v>106243</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7360,10 +7358,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>615955</v>
+        <v>616148</v>
       </c>
       <c r="R68" t="n">
-        <v>6646826</v>
+        <v>6646963</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7398,12 +7396,18 @@
           <t>2025-12-04</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>8 buketter</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7422,49 +7426,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129976707</v>
+        <v>129976713</v>
       </c>
       <c r="B69" t="n">
-        <v>98920</v>
+        <v>106243</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Hedmossen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>616125</v>
+        <v>616084</v>
       </c>
       <c r="R69" t="n">
-        <v>6647116</v>
+        <v>6647010</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>2 buketter</t>
+          <t>8 buketter</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7529,32 +7529,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129976683</v>
+        <v>129806158</v>
       </c>
       <c r="B70" t="n">
-        <v>91728</v>
+        <v>97983</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>615962</v>
+        <v>616104</v>
       </c>
       <c r="R70" t="n">
-        <v>6646716</v>
+        <v>6646974</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7594,12 +7594,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7623,6 +7623,103 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129976690</v>
+      </c>
+      <c r="B71" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Hedmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>616096</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6646883</v>
+      </c>
+      <c r="S71" t="n">
+        <v>15</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50796-2025 artfynd.xlsx
+++ b/artfynd/A 50796-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AZ71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806147</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806148</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976682</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976683</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976684</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976689</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806195</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806146</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806172</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806173</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806174</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806175</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806176</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806177</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806191</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806192</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806193</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806194</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2521,6 +2616,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976715</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2618,6 +2718,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976716</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2715,6 +2820,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976717</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2812,6 +2922,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806155</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2909,6 +3024,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806156</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3006,6 +3126,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806157</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3103,6 +3228,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976686</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3200,6 +3330,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976687</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3297,6 +3432,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976688</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3394,6 +3534,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976726</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3491,6 +3636,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976727</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3588,6 +3738,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806149</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3685,6 +3840,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806150</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3782,6 +3942,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806151</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3879,6 +4044,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806152</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3976,6 +4146,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976685</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4073,6 +4248,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976681</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4175,6 +4355,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806159</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4277,6 +4462,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806160</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4379,6 +4569,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806161</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4481,6 +4676,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806162</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4583,6 +4783,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806163</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4685,6 +4890,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806165</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4787,6 +4997,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806166</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4889,6 +5104,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806167</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4991,6 +5211,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806168</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5093,6 +5318,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806169</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5200,6 +5430,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976691</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5307,6 +5542,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976692</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5414,6 +5654,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976693</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5521,6 +5766,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976694</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5628,6 +5878,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976695</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5735,6 +5990,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976697</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5842,6 +6102,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976698</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5949,6 +6214,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976699</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6056,6 +6326,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976700</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6163,6 +6438,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976701</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6270,6 +6550,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976702</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6377,6 +6662,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976704</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6484,6 +6774,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976705</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6591,6 +6886,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976706</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6698,6 +6998,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976707</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6805,6 +7110,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976708</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6912,6 +7222,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976709</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7019,6 +7334,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976710</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7126,6 +7446,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976711</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7223,6 +7548,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806170</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7320,6 +7650,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806171</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7423,6 +7758,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976712</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7526,6 +7866,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976713</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7623,6 +7968,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806158</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7720,8 +8070,85 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976690</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>